--- a/research/traditional_assets/database/data/luxembourg/luxembourg_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_real_estate_general_diversified.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0686193600957969</v>
+        <v>0.06848200041171798</v>
       </c>
       <c r="C2">
-        <v>4405.293318064118</v>
+        <v>4362.606657933796</v>
       </c>
       <c r="D2">
-        <v>4268.793318064118</v>
+        <v>4294.644657933795</v>
       </c>
       <c r="E2">
-        <v>-5710.6</v>
+        <v>-5642.062000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>68.538</v>
       </c>
       <c r="G2">
         <v>136.5</v>
@@ -1445,28 +1445,28 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.447461399999999</v>
       </c>
       <c r="N2">
-        <v>88.54000000000001</v>
+        <v>85.09253860000001</v>
       </c>
       <c r="O2">
-        <v>22.081876</v>
+        <v>21.22207912684</v>
       </c>
       <c r="P2">
-        <v>66.458124</v>
+        <v>63.87045947316001</v>
       </c>
       <c r="Q2">
-        <v>63.318124</v>
+        <v>60.73045947316001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0686193600957969</v>
+        <v>0.06879237233506867</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313372</v>
+        <v>0.5310016705558585</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>25.68266609163485</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06848200041171798</v>
+        <v>0.06836715872763906</v>
       </c>
       <c r="C3">
-        <v>4362.606657933796</v>
+        <v>4315.923612338561</v>
       </c>
       <c r="D3">
-        <v>4294.644657933795</v>
+        <v>4316.499612338561</v>
       </c>
       <c r="E3">
-        <v>-5642.062000000001</v>
+        <v>-5573.524</v>
       </c>
       <c r="F3">
-        <v>68.538</v>
+        <v>137.076</v>
       </c>
       <c r="G3">
         <v>136.5</v>
@@ -1527,45 +1527,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M3">
-        <v>3.447461399999999</v>
+        <v>7.1005368</v>
       </c>
       <c r="N3">
-        <v>85.09253860000001</v>
+        <v>81.43946320000001</v>
       </c>
       <c r="O3">
-        <v>21.22207912684</v>
+        <v>20.31100212208</v>
       </c>
       <c r="P3">
-        <v>63.87045947316001</v>
+        <v>61.12846107792001</v>
       </c>
       <c r="Q3">
-        <v>60.73045947316001</v>
+        <v>57.98846107792001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06879237233506867</v>
+        <v>0.06896891543636639</v>
       </c>
       <c r="T3">
-        <v>0.5310016705558585</v>
+        <v>0.535078878438023</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>25.68266609163485</v>
+        <v>12.46947977228989</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06836715872763906</v>
+        <v>0.06827933864356013</v>
       </c>
       <c r="C4">
-        <v>4315.923612338561</v>
+        <v>4264.248891320785</v>
       </c>
       <c r="D4">
-        <v>4316.499612338561</v>
+        <v>4333.362891320785</v>
       </c>
       <c r="E4">
-        <v>-5573.524</v>
+        <v>-5504.986000000001</v>
       </c>
       <c r="F4">
-        <v>137.076</v>
+        <v>205.614</v>
       </c>
       <c r="G4">
         <v>136.5</v>
@@ -1609,45 +1609,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M4">
-        <v>7.1005368</v>
+        <v>11.000349</v>
       </c>
       <c r="N4">
-        <v>81.43946320000001</v>
+        <v>77.53965100000001</v>
       </c>
       <c r="O4">
-        <v>20.31100212208</v>
+        <v>19.3383889594</v>
       </c>
       <c r="P4">
-        <v>61.12846107792001</v>
+        <v>58.2012620406</v>
       </c>
       <c r="Q4">
-        <v>57.98846107792001</v>
+        <v>55.0612620406</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06896891543636639</v>
+        <v>0.06914909860160839</v>
       </c>
       <c r="T4">
-        <v>0.535078878438023</v>
+        <v>0.5392401524620878</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>12.46947977228989</v>
+        <v>8.048835541490547</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06827933864356013</v>
+        <v>0.06822004135948123</v>
       </c>
       <c r="C5">
-        <v>4264.248891320785</v>
+        <v>4207.171916136198</v>
       </c>
       <c r="D5">
-        <v>4333.362891320785</v>
+        <v>4344.823916136198</v>
       </c>
       <c r="E5">
-        <v>-5504.986000000001</v>
+        <v>-5436.448</v>
       </c>
       <c r="F5">
-        <v>205.614</v>
+        <v>274.152</v>
       </c>
       <c r="G5">
         <v>136.5</v>
@@ -1691,45 +1691,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M5">
-        <v>11.000349</v>
+        <v>15.1606056</v>
       </c>
       <c r="N5">
-        <v>77.53965100000001</v>
+        <v>73.37939440000001</v>
       </c>
       <c r="O5">
-        <v>19.3383889594</v>
+        <v>18.30082096336</v>
       </c>
       <c r="P5">
-        <v>58.2012620406</v>
+        <v>55.07857343664001</v>
       </c>
       <c r="Q5">
-        <v>55.0612620406</v>
+        <v>51.93857343664001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06914909860160839</v>
+        <v>0.06933303558279294</v>
       </c>
       <c r="T5">
-        <v>0.5392401524620878</v>
+        <v>0.5434881196949873</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.04015709999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.048835541490547</v>
+        <v>5.840136095882609</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06822004135948123</v>
+        <v>0.0681202116754023</v>
       </c>
       <c r="C6">
-        <v>4207.171916136198</v>
+        <v>4158.06663502051</v>
       </c>
       <c r="D6">
-        <v>4344.823916136198</v>
+        <v>4364.256635020511</v>
       </c>
       <c r="E6">
-        <v>-5436.448</v>
+        <v>-5367.91</v>
       </c>
       <c r="F6">
-        <v>274.152</v>
+        <v>342.6900000000001</v>
       </c>
       <c r="G6">
         <v>136.5</v>
@@ -1773,28 +1773,28 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M6">
-        <v>15.1606056</v>
+        <v>18.950757</v>
       </c>
       <c r="N6">
-        <v>73.37939440000001</v>
+        <v>69.58924300000001</v>
       </c>
       <c r="O6">
-        <v>18.30082096336</v>
+        <v>17.3555572042</v>
       </c>
       <c r="P6">
-        <v>55.07857343664001</v>
+        <v>52.23368579580001</v>
       </c>
       <c r="Q6">
-        <v>51.93857343664001</v>
+        <v>49.09368579580001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06933303558279294</v>
+        <v>0.06952084492147612</v>
       </c>
       <c r="T6">
-        <v>0.5434881196949873</v>
+        <v>0.5478255178170005</v>
       </c>
       <c r="U6">
         <v>0.0553</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>5.840136095882609</v>
+        <v>4.672108876706086</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0681202116754023</v>
+        <v>0.06829059799132339</v>
       </c>
       <c r="C7">
-        <v>4158.06663502051</v>
+        <v>4056.465503036995</v>
       </c>
       <c r="D7">
-        <v>4364.256635020511</v>
+        <v>4331.193503036995</v>
       </c>
       <c r="E7">
-        <v>-5367.91</v>
+        <v>-5299.372</v>
       </c>
       <c r="F7">
-        <v>342.6900000000001</v>
+        <v>411.2280000000001</v>
       </c>
       <c r="G7">
         <v>136.5</v>
@@ -1855,45 +1855,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M7">
-        <v>18.950757</v>
+        <v>25.2082764</v>
       </c>
       <c r="N7">
-        <v>69.58924300000001</v>
+        <v>63.3317236</v>
       </c>
       <c r="O7">
-        <v>17.3555572042</v>
+        <v>15.79493186584</v>
       </c>
       <c r="P7">
-        <v>52.23368579580001</v>
+        <v>47.53679173416</v>
       </c>
       <c r="Q7">
-        <v>49.09368579580001</v>
+        <v>44.39679173416</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06952084492147612</v>
+        <v>0.06971265020353552</v>
       </c>
       <c r="T7">
-        <v>0.5478255178170005</v>
+        <v>0.5522552010054395</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.04150818</v>
+        <v>0.04601178</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.672108876706086</v>
+        <v>3.512338511172465</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06829059799132339</v>
+        <v>0.06879274950724448</v>
       </c>
       <c r="C8">
-        <v>4056.465503036995</v>
+        <v>3893.336145765332</v>
       </c>
       <c r="D8">
-        <v>4331.193503036995</v>
+        <v>4236.602145765332</v>
       </c>
       <c r="E8">
-        <v>-5299.372</v>
+        <v>-5230.834000000001</v>
       </c>
       <c r="F8">
-        <v>411.228</v>
+        <v>479.766</v>
       </c>
       <c r="G8">
         <v>136.5</v>
@@ -1937,45 +1937,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M8">
-        <v>25.2082764</v>
+        <v>34.4951754</v>
       </c>
       <c r="N8">
-        <v>63.3317236</v>
+        <v>54.04482460000001</v>
       </c>
       <c r="O8">
-        <v>15.79493186584</v>
+        <v>13.47877925524</v>
       </c>
       <c r="P8">
-        <v>47.53679173416</v>
+        <v>40.56604534476</v>
       </c>
       <c r="Q8">
-        <v>44.39679173416</v>
+        <v>37.42604534476</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06971265020353552</v>
+        <v>0.06990858033037041</v>
       </c>
       <c r="T8">
-        <v>0.5522552010054395</v>
+        <v>0.5567801461979309</v>
       </c>
       <c r="U8">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.04601178</v>
+        <v>0.05396814</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.512338511172466</v>
+        <v>2.566735752849658</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06879274950724447</v>
+        <v>0.06905170662316557</v>
       </c>
       <c r="C9">
-        <v>3893.336145765336</v>
+        <v>3777.614586693611</v>
       </c>
       <c r="D9">
-        <v>4236.602145765336</v>
+        <v>4189.418586693611</v>
       </c>
       <c r="E9">
-        <v>-5230.834000000001</v>
+        <v>-5162.296</v>
       </c>
       <c r="F9">
-        <v>479.7660000000001</v>
+        <v>548.304</v>
       </c>
       <c r="G9">
         <v>136.5</v>
@@ -2019,45 +2019,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M9">
-        <v>34.49517540000001</v>
+        <v>41.5614432</v>
       </c>
       <c r="N9">
-        <v>54.0448246</v>
+        <v>46.97855680000001</v>
       </c>
       <c r="O9">
-        <v>13.47877925524</v>
+        <v>11.71645206592</v>
       </c>
       <c r="P9">
-        <v>40.56604534476</v>
+        <v>35.26210473408</v>
       </c>
       <c r="Q9">
-        <v>37.42604534476</v>
+        <v>32.12210473408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06990858033037041</v>
+        <v>0.07010876980778866</v>
       </c>
       <c r="T9">
-        <v>0.5567801461979309</v>
+        <v>0.5614034597641722</v>
       </c>
       <c r="U9">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.566735752849658</v>
+        <v>2.130339881941347</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06905170662316557</v>
+        <v>0.07006501673908665</v>
       </c>
       <c r="C10">
-        <v>3777.614586693611</v>
+        <v>3534.125945638162</v>
       </c>
       <c r="D10">
-        <v>4189.418586693611</v>
+        <v>4014.467945638161</v>
       </c>
       <c r="E10">
-        <v>-5162.296</v>
+        <v>-5093.758000000001</v>
       </c>
       <c r="F10">
-        <v>548.304</v>
+        <v>616.842</v>
       </c>
       <c r="G10">
         <v>136.5</v>
@@ -2101,45 +2101,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M10">
-        <v>41.5614432</v>
+        <v>55.51578</v>
       </c>
       <c r="N10">
-        <v>46.97855680000001</v>
+        <v>33.02422000000001</v>
       </c>
       <c r="O10">
-        <v>11.71645206592</v>
+        <v>8.236240468000002</v>
       </c>
       <c r="P10">
-        <v>35.26210473408</v>
+        <v>24.787979532</v>
       </c>
       <c r="Q10">
-        <v>32.12210473408</v>
+        <v>21.647979532</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07010876980778866</v>
+        <v>0.07031335905394137</v>
       </c>
       <c r="T10">
-        <v>0.5614034597641722</v>
+        <v>0.5661283846175836</v>
       </c>
       <c r="U10">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.130339881941347</v>
+        <v>1.594861857295349</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07006501673908665</v>
+        <v>0.0749966955383892</v>
       </c>
       <c r="C11">
-        <v>3534.125945638162</v>
+        <v>2787.495233675194</v>
       </c>
       <c r="D11">
-        <v>4014.467945638161</v>
+        <v>3336.375233675195</v>
       </c>
       <c r="E11">
-        <v>-5093.758000000001</v>
+        <v>-5025.22</v>
       </c>
       <c r="F11">
-        <v>616.842</v>
+        <v>685.38</v>
       </c>
       <c r="G11">
         <v>136.5</v>
@@ -2183,45 +2183,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M11">
-        <v>55.51578</v>
+        <v>100.613784</v>
       </c>
       <c r="N11">
-        <v>33.02422000000001</v>
+        <v>-12.073784</v>
       </c>
       <c r="O11">
-        <v>8.236240468000002</v>
+        <v>-3.011201729600001</v>
       </c>
       <c r="P11">
-        <v>24.787979532</v>
+        <v>-9.062582270400002</v>
       </c>
       <c r="Q11">
-        <v>21.647979532</v>
+        <v>-12.2025822704</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07031335905394137</v>
+        <v>0.07059837752309536</v>
       </c>
       <c r="T11">
-        <v>0.5661283846175836</v>
+        <v>0.5727107973001241</v>
       </c>
       <c r="U11">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V11">
-        <v>0.2494</v>
+        <v>0.2194716779561735</v>
       </c>
       <c r="W11">
-        <v>0.06755399999999999</v>
+        <v>0.1145815576760337</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y11">
-        <v>1.594861857295349</v>
+        <v>0.8799987087256355</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0749966955383892</v>
+        <v>0.08208137829511528</v>
       </c>
       <c r="C12">
-        <v>2787.495233675194</v>
+        <v>2067.461584978492</v>
       </c>
       <c r="D12">
-        <v>3336.375233675195</v>
+        <v>2684.879584978492</v>
       </c>
       <c r="E12">
-        <v>-5025.22</v>
+        <v>-4956.682000000001</v>
       </c>
       <c r="F12">
-        <v>685.3800000000001</v>
+        <v>753.918</v>
       </c>
       <c r="G12">
         <v>136.5</v>
@@ -2265,45 +2265,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M12">
-        <v>100.613784</v>
+        <v>151.3867344</v>
       </c>
       <c r="N12">
-        <v>-12.07378400000002</v>
+        <v>-62.84673439999999</v>
       </c>
       <c r="O12">
-        <v>-3.011201729600005</v>
+        <v>-15.67397555936</v>
       </c>
       <c r="P12">
-        <v>-9.062582270400013</v>
+        <v>-47.17275884063999</v>
       </c>
       <c r="Q12">
-        <v>-12.20258227040001</v>
+        <v>-50.31275884063999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07059837752309536</v>
+        <v>0.0710283399185527</v>
       </c>
       <c r="T12">
-        <v>0.5727107973001241</v>
+        <v>0.5826406447702706</v>
       </c>
       <c r="U12">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.2194716779561735</v>
+        <v>0.145864009072647</v>
       </c>
       <c r="W12">
-        <v>0.1145815576760337</v>
+        <v>0.1715105069782125</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y12">
-        <v>0.8799987087256353</v>
+        <v>0.584859699569555</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08208137829511528</v>
+        <v>0.08363137829511529</v>
       </c>
       <c r="C13">
-        <v>2067.461584978492</v>
+        <v>1888.92063123324</v>
       </c>
       <c r="D13">
-        <v>2684.879584978492</v>
+        <v>2574.87663123324</v>
       </c>
       <c r="E13">
-        <v>-4956.682000000001</v>
+        <v>-4888.144</v>
       </c>
       <c r="F13">
-        <v>753.918</v>
+        <v>822.456</v>
       </c>
       <c r="G13">
         <v>136.5</v>
@@ -2347,37 +2347,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M13">
-        <v>151.3867344</v>
+        <v>165.1491648</v>
       </c>
       <c r="N13">
-        <v>-62.84673439999999</v>
+        <v>-76.60916480000002</v>
       </c>
       <c r="O13">
-        <v>-15.67397555936</v>
+        <v>-19.10632570112001</v>
       </c>
       <c r="P13">
-        <v>-47.17275884063999</v>
+        <v>-57.50283909888001</v>
       </c>
       <c r="Q13">
-        <v>-50.31275884063999</v>
+        <v>-60.64283909888001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0710283399185527</v>
+        <v>0.07131502559944536</v>
       </c>
       <c r="T13">
-        <v>0.5826406447702706</v>
+        <v>0.5892615611881146</v>
       </c>
       <c r="U13">
         <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.145864009072647</v>
+        <v>0.1337086749832597</v>
       </c>
       <c r="W13">
-        <v>0.1715105069782125</v>
+        <v>0.1739512980633615</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.584859699569555</v>
+        <v>0.5361213912720919</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08363137829511529</v>
+        <v>0.08978572441424157</v>
       </c>
       <c r="C14">
-        <v>1888.92063123324</v>
+        <v>1460.113880094326</v>
       </c>
       <c r="D14">
-        <v>2574.87663123324</v>
+        <v>2214.607880094326</v>
       </c>
       <c r="E14">
-        <v>-4888.144</v>
+        <v>-4819.606000000001</v>
       </c>
       <c r="F14">
-        <v>822.456</v>
+        <v>890.994</v>
       </c>
       <c r="G14">
         <v>136.5</v>
@@ -2429,45 +2429,45 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M14">
-        <v>165.1491648</v>
+        <v>210.0963852</v>
       </c>
       <c r="N14">
-        <v>-76.60916480000002</v>
+        <v>-121.5563852</v>
       </c>
       <c r="O14">
-        <v>-19.10632570112001</v>
+        <v>-30.31616246888</v>
       </c>
       <c r="P14">
-        <v>-57.50283909888001</v>
+        <v>-91.24022273112001</v>
       </c>
       <c r="Q14">
-        <v>-60.64283909888001</v>
+        <v>-94.38022273112001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07131502559944536</v>
+        <v>0.07167076855935424</v>
       </c>
       <c r="T14">
-        <v>0.5892615611881146</v>
+        <v>0.597477333934278</v>
       </c>
       <c r="U14">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.1337086749832597</v>
+        <v>0.1051035503489472</v>
       </c>
       <c r="W14">
-        <v>0.1739512980633615</v>
+        <v>0.2110165828277183</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.5361213912720919</v>
+        <v>0.4214256228907265</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08978572441424157</v>
+        <v>0.09168572441424155</v>
       </c>
       <c r="C15">
-        <v>1460.113880094326</v>
+        <v>1299.875138177451</v>
       </c>
       <c r="D15">
-        <v>2214.607880094326</v>
+        <v>2122.907138177452</v>
       </c>
       <c r="E15">
-        <v>-4819.606000000001</v>
+        <v>-4751.068</v>
       </c>
       <c r="F15">
-        <v>890.994</v>
+        <v>959.5320000000002</v>
       </c>
       <c r="G15">
         <v>136.5</v>
@@ -2511,37 +2511,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M15">
-        <v>210.0963852</v>
+        <v>226.2576456</v>
       </c>
       <c r="N15">
-        <v>-121.5563852</v>
+        <v>-137.7176456</v>
       </c>
       <c r="O15">
-        <v>-30.31616246888</v>
+        <v>-34.34678081264001</v>
       </c>
       <c r="P15">
-        <v>-91.24022273112001</v>
+        <v>-103.37086478736</v>
       </c>
       <c r="Q15">
-        <v>-94.38022273112001</v>
+        <v>-106.51086478736</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07167076855935424</v>
+        <v>0.07197159144957928</v>
       </c>
       <c r="T15">
-        <v>0.597477333934278</v>
+        <v>0.6044247447939789</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.1051035503489472</v>
+        <v>0.09759615389545094</v>
       </c>
       <c r="W15">
-        <v>0.2110165828277183</v>
+        <v>0.2127868269114527</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.4214256228907265</v>
+        <v>0.391323792684246</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09168572441424155</v>
+        <v>0.09358572441424157</v>
       </c>
       <c r="C16">
-        <v>1299.875138177451</v>
+        <v>1146.9285912321</v>
       </c>
       <c r="D16">
-        <v>2122.907138177452</v>
+        <v>2038.4985912321</v>
       </c>
       <c r="E16">
-        <v>-4751.068</v>
+        <v>-4682.530000000001</v>
       </c>
       <c r="F16">
-        <v>959.5320000000002</v>
+        <v>1028.07</v>
       </c>
       <c r="G16">
         <v>136.5</v>
@@ -2593,37 +2593,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M16">
-        <v>226.2576456</v>
+        <v>242.418906</v>
       </c>
       <c r="N16">
-        <v>-137.7176456</v>
+        <v>-153.878906</v>
       </c>
       <c r="O16">
-        <v>-34.34678081264001</v>
+        <v>-38.37739915640001</v>
       </c>
       <c r="P16">
-        <v>-103.37086478736</v>
+        <v>-115.5015068436</v>
       </c>
       <c r="Q16">
-        <v>-106.51086478736</v>
+        <v>-118.6415068436</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07197159144957928</v>
+        <v>0.07227949252545669</v>
       </c>
       <c r="T16">
-        <v>0.6044247447939789</v>
+        <v>0.6115356241444965</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.09759615389545094</v>
+        <v>0.09108974363575421</v>
       </c>
       <c r="W16">
-        <v>0.2127868269114527</v>
+        <v>0.2143210384506892</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.391323792684246</v>
+        <v>0.3652355398386296</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09358572441424154</v>
+        <v>0.09548572441424155</v>
       </c>
       <c r="C17">
-        <v>1146.9285912321</v>
+        <v>1000.437670770488</v>
       </c>
       <c r="D17">
-        <v>2038.4985912321</v>
+        <v>1960.545670770488</v>
       </c>
       <c r="E17">
-        <v>-4682.530000000001</v>
+        <v>-4613.992</v>
       </c>
       <c r="F17">
-        <v>1028.07</v>
+        <v>1096.608</v>
       </c>
       <c r="G17">
         <v>136.5</v>
@@ -2675,37 +2675,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M17">
-        <v>242.418906</v>
+        <v>258.5801664</v>
       </c>
       <c r="N17">
-        <v>-153.878906</v>
+        <v>-170.0401664</v>
       </c>
       <c r="O17">
-        <v>-38.3773991564</v>
+        <v>-42.40801750015999</v>
       </c>
       <c r="P17">
-        <v>-115.5015068436</v>
+        <v>-127.63214889984</v>
       </c>
       <c r="Q17">
-        <v>-118.6415068436</v>
+        <v>-130.77214889984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07227949252545668</v>
+        <v>0.07259472457933117</v>
       </c>
       <c r="T17">
-        <v>0.6115356241444964</v>
+        <v>0.6188158101462166</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.09108974363575423</v>
+        <v>0.0853966346585196</v>
       </c>
       <c r="W17">
-        <v>0.2143210384506891</v>
+        <v>0.2156634735475211</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3652355398386297</v>
+        <v>0.3424083185987153</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09548572441424155</v>
+        <v>0.09738572441424156</v>
       </c>
       <c r="C18">
-        <v>1000.437670770488</v>
+        <v>859.6890579166027</v>
       </c>
       <c r="D18">
-        <v>1960.545670770488</v>
+        <v>1888.335057916603</v>
       </c>
       <c r="E18">
-        <v>-4613.992</v>
+        <v>-4545.454</v>
       </c>
       <c r="F18">
-        <v>1096.608</v>
+        <v>1165.146</v>
       </c>
       <c r="G18">
         <v>136.5</v>
@@ -2757,37 +2757,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M18">
-        <v>258.5801664</v>
+        <v>274.7414268000001</v>
       </c>
       <c r="N18">
-        <v>-170.0401664</v>
+        <v>-186.2014268</v>
       </c>
       <c r="O18">
-        <v>-42.40801750015999</v>
+        <v>-46.43863584392001</v>
       </c>
       <c r="P18">
-        <v>-127.63214889984</v>
+        <v>-139.76279095608</v>
       </c>
       <c r="Q18">
-        <v>-130.77214889984</v>
+        <v>-142.90279095608</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07259472457933117</v>
+        <v>0.07291755258631107</v>
       </c>
       <c r="T18">
-        <v>0.6188158101462166</v>
+        <v>0.6262714223166529</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.0853966346585196</v>
+        <v>0.08037330320801842</v>
       </c>
       <c r="W18">
-        <v>0.2156634735475211</v>
+        <v>0.2168479751035493</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3424083185987153</v>
+        <v>0.3222666527987909</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09738572441424156</v>
+        <v>0.09928572441424158</v>
       </c>
       <c r="C19">
-        <v>859.6890579166027</v>
+        <v>724.0707921198057</v>
       </c>
       <c r="D19">
-        <v>1888.335057916603</v>
+        <v>1821.254792119806</v>
       </c>
       <c r="E19">
-        <v>-4545.454</v>
+        <v>-4476.916</v>
       </c>
       <c r="F19">
-        <v>1165.146</v>
+        <v>1233.684</v>
       </c>
       <c r="G19">
         <v>136.5</v>
@@ -2839,37 +2839,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M19">
-        <v>274.7414268000001</v>
+        <v>290.9026872000001</v>
       </c>
       <c r="N19">
-        <v>-186.2014268</v>
+        <v>-202.3626872</v>
       </c>
       <c r="O19">
-        <v>-46.43863584392001</v>
+        <v>-50.46925418768001</v>
       </c>
       <c r="P19">
-        <v>-139.76279095608</v>
+        <v>-151.89343301232</v>
       </c>
       <c r="Q19">
-        <v>-142.90279095608</v>
+        <v>-155.03343301232</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07291755258631107</v>
+        <v>0.07324825444711974</v>
       </c>
       <c r="T19">
-        <v>0.6262714223166529</v>
+        <v>0.6339088786863681</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.08037330320801842</v>
+        <v>0.07590811969646184</v>
       </c>
       <c r="W19">
-        <v>0.2168479751035493</v>
+        <v>0.2179008653755743</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3222666527987909</v>
+        <v>0.3043629498655247</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09928572441424158</v>
+        <v>0.1011857244142416</v>
       </c>
       <c r="C20">
-        <v>724.0707921198059</v>
+        <v>593.0548857346396</v>
       </c>
       <c r="D20">
-        <v>1821.254792119806</v>
+        <v>1758.77688573464</v>
       </c>
       <c r="E20">
-        <v>-4476.916</v>
+        <v>-4408.378000000001</v>
       </c>
       <c r="F20">
-        <v>1233.684</v>
+        <v>1302.222</v>
       </c>
       <c r="G20">
         <v>136.5</v>
@@ -2921,37 +2921,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M20">
-        <v>290.9026872</v>
+        <v>307.0639476</v>
       </c>
       <c r="N20">
-        <v>-202.3626872</v>
+        <v>-218.5239476</v>
       </c>
       <c r="O20">
-        <v>-50.46925418768</v>
+        <v>-54.49987253144</v>
       </c>
       <c r="P20">
-        <v>-151.89343301232</v>
+        <v>-164.02407506856</v>
       </c>
       <c r="Q20">
-        <v>-155.03343301232</v>
+        <v>-167.16407506856</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07324825444711974</v>
+        <v>0.07358712178597307</v>
       </c>
       <c r="T20">
-        <v>0.6339088786863681</v>
+        <v>0.6417349142257061</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07590811969646186</v>
+        <v>0.07191295550191122</v>
       </c>
       <c r="W20">
-        <v>0.2179008653755743</v>
+        <v>0.2188429250926493</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3043629498655247</v>
+        <v>0.2883438472410235</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1011857244142416</v>
+        <v>0.1030857244142416</v>
       </c>
       <c r="C21">
-        <v>593.0548857346396</v>
+        <v>466.1833983420099</v>
       </c>
       <c r="D21">
-        <v>1758.77688573464</v>
+        <v>1700.44339834201</v>
       </c>
       <c r="E21">
-        <v>-4408.378000000001</v>
+        <v>-4339.84</v>
       </c>
       <c r="F21">
-        <v>1302.222</v>
+        <v>1370.76</v>
       </c>
       <c r="G21">
         <v>136.5</v>
@@ -3003,37 +3003,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M21">
-        <v>307.0639476</v>
+        <v>323.2252080000001</v>
       </c>
       <c r="N21">
-        <v>-218.5239476</v>
+        <v>-234.685208</v>
       </c>
       <c r="O21">
-        <v>-54.49987253144</v>
+        <v>-58.53049087520002</v>
       </c>
       <c r="P21">
-        <v>-164.02407506856</v>
+        <v>-176.1547171248</v>
       </c>
       <c r="Q21">
-        <v>-167.16407506856</v>
+        <v>-179.2947171248</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07358712178597307</v>
+        <v>0.07393446080829773</v>
       </c>
       <c r="T21">
-        <v>0.6417349142257061</v>
+        <v>0.6497566006535274</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.07191295550191122</v>
+        <v>0.06831730772681566</v>
       </c>
       <c r="W21">
-        <v>0.2188429250926493</v>
+        <v>0.2196907788380169</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2883438472410235</v>
+        <v>0.2739266548789722</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1030857244142416</v>
+        <v>0.1049857244142416</v>
       </c>
       <c r="C22">
-        <v>466.1833983420099</v>
+        <v>343.0571933512738</v>
       </c>
       <c r="D22">
-        <v>1700.44339834201</v>
+        <v>1645.855193351274</v>
       </c>
       <c r="E22">
-        <v>-4339.84</v>
+        <v>-4271.302</v>
       </c>
       <c r="F22">
-        <v>1370.76</v>
+        <v>1439.298</v>
       </c>
       <c r="G22">
         <v>136.5</v>
@@ -3085,37 +3085,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M22">
-        <v>323.2252080000001</v>
+        <v>339.3864684000001</v>
       </c>
       <c r="N22">
-        <v>-234.685208</v>
+        <v>-250.8464684</v>
       </c>
       <c r="O22">
-        <v>-58.53049087520002</v>
+        <v>-62.56110921896001</v>
       </c>
       <c r="P22">
-        <v>-176.1547171248</v>
+        <v>-188.28535918104</v>
       </c>
       <c r="Q22">
-        <v>-179.2947171248</v>
+        <v>-191.42535918104</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07393446080829773</v>
+        <v>0.07429059322359263</v>
       </c>
       <c r="T22">
-        <v>0.6497566006535274</v>
+        <v>0.6579813677504075</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.06831730772681566</v>
+        <v>0.06506410259696729</v>
       </c>
       <c r="W22">
-        <v>0.2196907788380169</v>
+        <v>0.2204578846076351</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2739266548789722</v>
+        <v>0.260882528456164</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1049857244142416</v>
+        <v>0.1068857244142416</v>
       </c>
       <c r="C23">
-        <v>343.057193351274</v>
+        <v>223.3267928787609</v>
       </c>
       <c r="D23">
-        <v>1645.855193351274</v>
+        <v>1594.662792878761</v>
       </c>
       <c r="E23">
-        <v>-4271.302000000001</v>
+        <v>-4202.764</v>
       </c>
       <c r="F23">
-        <v>1439.298</v>
+        <v>1507.836</v>
       </c>
       <c r="G23">
         <v>136.5</v>
@@ -3167,37 +3167,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M23">
-        <v>339.3864684</v>
+        <v>355.5477288</v>
       </c>
       <c r="N23">
-        <v>-250.8464684</v>
+        <v>-267.0077288</v>
       </c>
       <c r="O23">
-        <v>-62.56110921896</v>
+        <v>-66.59172756272</v>
       </c>
       <c r="P23">
-        <v>-188.28535918104</v>
+        <v>-200.41600123728</v>
       </c>
       <c r="Q23">
-        <v>-191.42535918104</v>
+        <v>-203.55600123728</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07429059322359263</v>
+        <v>0.07465585723927973</v>
       </c>
       <c r="T23">
-        <v>0.6579813677504075</v>
+        <v>0.6664170263113101</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06506410259696731</v>
+        <v>0.06210664338801424</v>
       </c>
       <c r="W23">
-        <v>0.2204578846076351</v>
+        <v>0.2211552534891063</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.260882528456164</v>
+        <v>0.2490242317081566</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1068857244142416</v>
+        <v>0.1087857244142416</v>
       </c>
       <c r="C24">
-        <v>223.3267928787609</v>
+        <v>106.6848878328642</v>
       </c>
       <c r="D24">
-        <v>1594.662792878761</v>
+        <v>1546.558887832864</v>
       </c>
       <c r="E24">
-        <v>-4202.764</v>
+        <v>-4134.226000000001</v>
       </c>
       <c r="F24">
-        <v>1507.836</v>
+        <v>1576.374</v>
       </c>
       <c r="G24">
         <v>136.5</v>
@@ -3249,37 +3249,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M24">
-        <v>355.5477288</v>
+        <v>371.7089892</v>
       </c>
       <c r="N24">
-        <v>-267.0077288</v>
+        <v>-283.1689892</v>
       </c>
       <c r="O24">
-        <v>-66.59172756272</v>
+        <v>-70.62234590648001</v>
       </c>
       <c r="P24">
-        <v>-200.41600123728</v>
+        <v>-212.54664329352</v>
       </c>
       <c r="Q24">
-        <v>-203.55600123728</v>
+        <v>-215.68664329352</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07465585723927973</v>
+        <v>0.07503060863199765</v>
       </c>
       <c r="T24">
-        <v>0.6664170263113101</v>
+        <v>0.6750717928867817</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06210664338801424</v>
+        <v>0.05940635454505711</v>
       </c>
       <c r="W24">
-        <v>0.2211552534891063</v>
+        <v>0.2217919815982755</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2490242317081566</v>
+        <v>0.2381970911991063</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1087857244142416</v>
+        <v>0.1106857244142416</v>
       </c>
       <c r="C25">
-        <v>106.6848878328642</v>
+        <v>-7.139836071499985</v>
       </c>
       <c r="D25">
-        <v>1546.558887832864</v>
+        <v>1501.2721639285</v>
       </c>
       <c r="E25">
-        <v>-4134.226000000001</v>
+        <v>-4065.688</v>
       </c>
       <c r="F25">
-        <v>1576.374</v>
+        <v>1644.912</v>
       </c>
       <c r="G25">
         <v>136.5</v>
@@ -3331,37 +3331,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M25">
-        <v>371.7089892</v>
+        <v>387.8702496000001</v>
       </c>
       <c r="N25">
-        <v>-283.1689892</v>
+        <v>-299.3302496000001</v>
       </c>
       <c r="O25">
-        <v>-70.62234590648001</v>
+        <v>-74.65296425024002</v>
       </c>
       <c r="P25">
-        <v>-212.54664329352</v>
+        <v>-224.67728534976</v>
       </c>
       <c r="Q25">
-        <v>-215.68664329352</v>
+        <v>-227.81728534976</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07503060863199765</v>
+        <v>0.0754152219034713</v>
       </c>
       <c r="T25">
-        <v>0.6750717928867817</v>
+        <v>0.6839543164773972</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05940635454505711</v>
+        <v>0.05693108977234639</v>
       </c>
       <c r="W25">
-        <v>0.2217919815982755</v>
+        <v>0.2223756490316807</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2381970911991063</v>
+        <v>0.2282722123991435</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1106857244142416</v>
+        <v>0.1125857244142416</v>
       </c>
       <c r="C26">
-        <v>-7.139836071499758</v>
+        <v>-118.3878184289856</v>
       </c>
       <c r="D26">
-        <v>1501.2721639285</v>
+        <v>1458.562181571014</v>
       </c>
       <c r="E26">
-        <v>-4065.688</v>
+        <v>-3997.150000000001</v>
       </c>
       <c r="F26">
-        <v>1644.912</v>
+        <v>1713.45</v>
       </c>
       <c r="G26">
         <v>136.5</v>
@@ -3413,37 +3413,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M26">
-        <v>387.8702496</v>
+        <v>404.03151</v>
       </c>
       <c r="N26">
-        <v>-299.3302496</v>
+        <v>-315.49151</v>
       </c>
       <c r="O26">
-        <v>-74.65296425024</v>
+        <v>-78.683582594</v>
       </c>
       <c r="P26">
-        <v>-224.67728534976</v>
+        <v>-236.807927406</v>
       </c>
       <c r="Q26">
-        <v>-227.81728534976</v>
+        <v>-239.947927406</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0754152219034713</v>
+        <v>0.0758100915288509</v>
       </c>
       <c r="T26">
-        <v>0.6839543164773972</v>
+        <v>0.6930737073637625</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05693108977234639</v>
+        <v>0.05465384618145253</v>
       </c>
       <c r="W26">
-        <v>0.2223756490316807</v>
+        <v>0.2229126230704135</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2282722123991435</v>
+        <v>0.2191413239031778</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1125857244142416</v>
+        <v>0.1144857244142416</v>
       </c>
       <c r="C27">
-        <v>-118.3878184289856</v>
+        <v>-227.2728944570624</v>
       </c>
       <c r="D27">
-        <v>1458.562181571014</v>
+        <v>1418.215105542938</v>
       </c>
       <c r="E27">
-        <v>-3997.150000000001</v>
+        <v>-3928.612</v>
       </c>
       <c r="F27">
-        <v>1713.45</v>
+        <v>1781.988</v>
       </c>
       <c r="G27">
         <v>136.5</v>
@@ -3495,37 +3495,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M27">
-        <v>404.03151</v>
+        <v>420.1927704</v>
       </c>
       <c r="N27">
-        <v>-315.49151</v>
+        <v>-331.6527704</v>
       </c>
       <c r="O27">
-        <v>-78.683582594</v>
+        <v>-82.71420093776001</v>
       </c>
       <c r="P27">
-        <v>-236.807927406</v>
+        <v>-248.93856946224</v>
       </c>
       <c r="Q27">
-        <v>-239.947927406</v>
+        <v>-252.07856946224</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0758100915288509</v>
+        <v>0.07621563330626782</v>
       </c>
       <c r="T27">
-        <v>0.6930737073637625</v>
+        <v>0.7024395682740837</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05465384618145253</v>
+        <v>0.05255177517447359</v>
       </c>
       <c r="W27">
-        <v>0.2229126230704135</v>
+        <v>0.2234082914138591</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2191413239031778</v>
+        <v>0.2107128114453632</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1144857244142416</v>
+        <v>0.1163857244142416</v>
       </c>
       <c r="C28">
-        <v>-227.2728944570624</v>
+        <v>-333.985875629146</v>
       </c>
       <c r="D28">
-        <v>1418.215105542938</v>
+        <v>1380.040124370854</v>
       </c>
       <c r="E28">
-        <v>-3928.612</v>
+        <v>-3860.074000000001</v>
       </c>
       <c r="F28">
-        <v>1781.988</v>
+        <v>1850.526</v>
       </c>
       <c r="G28">
         <v>136.5</v>
@@ -3577,37 +3577,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M28">
-        <v>420.1927704</v>
+        <v>436.3540308</v>
       </c>
       <c r="N28">
-        <v>-331.6527704</v>
+        <v>-347.8140308</v>
       </c>
       <c r="O28">
-        <v>-82.71420093776001</v>
+        <v>-86.74481928152001</v>
       </c>
       <c r="P28">
-        <v>-248.93856946224</v>
+        <v>-261.06921151848</v>
       </c>
       <c r="Q28">
-        <v>-252.07856946224</v>
+        <v>-264.20921151848</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07621563330626782</v>
+        <v>0.07663228581731257</v>
       </c>
       <c r="T28">
-        <v>0.7024395682740837</v>
+        <v>0.7120620281134546</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05255177517447359</v>
+        <v>0.05060541313097457</v>
       </c>
       <c r="W28">
-        <v>0.2234082914138591</v>
+        <v>0.2238672435837162</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2107128114453632</v>
+        <v>0.2029086332436831</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1163857244142416</v>
+        <v>0.1182857244142416</v>
       </c>
       <c r="C29">
-        <v>-333.985875629146</v>
+        <v>-438.6975671731532</v>
       </c>
       <c r="D29">
-        <v>1380.040124370854</v>
+        <v>1343.866432826847</v>
       </c>
       <c r="E29">
-        <v>-3860.074000000001</v>
+        <v>-3791.536</v>
       </c>
       <c r="F29">
-        <v>1850.526</v>
+        <v>1919.064</v>
       </c>
       <c r="G29">
         <v>136.5</v>
@@ -3659,37 +3659,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M29">
-        <v>436.3540308</v>
+        <v>452.5152912000001</v>
       </c>
       <c r="N29">
-        <v>-347.8140308</v>
+        <v>-363.9752912000001</v>
       </c>
       <c r="O29">
-        <v>-86.74481928152001</v>
+        <v>-90.77543762528002</v>
       </c>
       <c r="P29">
-        <v>-261.06921151848</v>
+        <v>-273.1998535747201</v>
       </c>
       <c r="Q29">
-        <v>-264.20921151848</v>
+        <v>-276.3398535747201</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07663228581731257</v>
+        <v>0.07706051200921971</v>
       </c>
       <c r="T29">
-        <v>0.7120620281134546</v>
+        <v>0.7219517785039195</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05060541313097457</v>
+        <v>0.04879807694772547</v>
       </c>
       <c r="W29">
-        <v>0.2238672435837162</v>
+        <v>0.2242934134557263</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2029086332436831</v>
+        <v>0.1956618963421229</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1182857244142416</v>
+        <v>0.1201857244142416</v>
       </c>
       <c r="C30">
-        <v>-438.6975671731532</v>
+        <v>-541.5613231226664</v>
       </c>
       <c r="D30">
-        <v>1343.866432826847</v>
+        <v>1309.540676877334</v>
       </c>
       <c r="E30">
-        <v>-3791.536</v>
+        <v>-3722.998</v>
       </c>
       <c r="F30">
-        <v>1919.064</v>
+        <v>1987.602</v>
       </c>
       <c r="G30">
         <v>136.5</v>
@@ -3741,37 +3741,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M30">
-        <v>452.5152912000001</v>
+        <v>468.6765516000001</v>
       </c>
       <c r="N30">
-        <v>-363.9752912000001</v>
+        <v>-380.1365516000001</v>
       </c>
       <c r="O30">
-        <v>-90.77543762528002</v>
+        <v>-94.80605596904002</v>
       </c>
       <c r="P30">
-        <v>-273.1998535747201</v>
+        <v>-285.3304956309601</v>
       </c>
       <c r="Q30">
-        <v>-276.3398535747201</v>
+        <v>-288.47049563096</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07706051200921971</v>
+        <v>0.07750080091075801</v>
       </c>
       <c r="T30">
-        <v>0.7219517785039195</v>
+        <v>0.7321201134124252</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04879807694772547</v>
+        <v>0.04711538463918321</v>
       </c>
       <c r="W30">
-        <v>0.2242934134557263</v>
+        <v>0.2246901923020806</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1956618963421229</v>
+        <v>0.1889149343992912</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1201857244142416</v>
+        <v>0.1220857244142416</v>
       </c>
       <c r="C31">
-        <v>-541.5613231226646</v>
+        <v>-642.7152195459087</v>
       </c>
       <c r="D31">
-        <v>1309.540676877335</v>
+        <v>1276.924780454091</v>
       </c>
       <c r="E31">
-        <v>-3722.998000000001</v>
+        <v>-3654.46</v>
       </c>
       <c r="F31">
-        <v>1987.602</v>
+        <v>2056.14</v>
       </c>
       <c r="G31">
         <v>136.5</v>
@@ -3823,37 +3823,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M31">
-        <v>468.6765516</v>
+        <v>484.837812</v>
       </c>
       <c r="N31">
-        <v>-380.1365516</v>
+        <v>-396.297812</v>
       </c>
       <c r="O31">
-        <v>-94.80605596903999</v>
+        <v>-98.8366743128</v>
       </c>
       <c r="P31">
-        <v>-285.3304956309599</v>
+        <v>-297.4611376872</v>
       </c>
       <c r="Q31">
-        <v>-288.4704956309599</v>
+        <v>-300.6011376872</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07750080091075801</v>
+        <v>0.07795366949519741</v>
       </c>
       <c r="T31">
-        <v>0.7321201134124252</v>
+        <v>0.7425789721754599</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04711538463918322</v>
+        <v>0.04554487181787711</v>
       </c>
       <c r="W31">
-        <v>0.2246901923020806</v>
+        <v>0.2250605192253446</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1889149343992912</v>
+        <v>0.1826177699193149</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1220857244142416</v>
+        <v>0.1239857244142415</v>
       </c>
       <c r="C32">
-        <v>-642.7152195459087</v>
+        <v>-742.2839109034333</v>
       </c>
       <c r="D32">
-        <v>1276.924780454091</v>
+        <v>1245.894089096567</v>
       </c>
       <c r="E32">
-        <v>-3654.46</v>
+        <v>-3585.922</v>
       </c>
       <c r="F32">
-        <v>2056.14</v>
+        <v>2124.678</v>
       </c>
       <c r="G32">
         <v>136.5</v>
@@ -3905,37 +3905,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M32">
-        <v>484.837812</v>
+        <v>500.9990724</v>
       </c>
       <c r="N32">
-        <v>-396.297812</v>
+        <v>-412.4590724</v>
       </c>
       <c r="O32">
-        <v>-98.8366743128</v>
+        <v>-102.86729265656</v>
       </c>
       <c r="P32">
-        <v>-297.4611376872</v>
+        <v>-309.59177974344</v>
       </c>
       <c r="Q32">
-        <v>-300.6011376872</v>
+        <v>-312.73177974344</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07795366949519741</v>
+        <v>0.07841966470527273</v>
       </c>
       <c r="T32">
-        <v>0.7425789721754599</v>
+        <v>0.7533409862649593</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04554487181787711</v>
+        <v>0.04407568240439721</v>
       </c>
       <c r="W32">
-        <v>0.2250605192253446</v>
+        <v>0.2254069540890432</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1826177699193149</v>
+        <v>0.1767268741154659</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1239857244142415</v>
+        <v>0.1258857244142416</v>
       </c>
       <c r="C33">
-        <v>-742.2839109034333</v>
+        <v>-840.3802221579983</v>
       </c>
       <c r="D33">
-        <v>1245.894089096567</v>
+        <v>1216.335777842002</v>
       </c>
       <c r="E33">
-        <v>-3585.922</v>
+        <v>-3517.384</v>
       </c>
       <c r="F33">
-        <v>2124.678</v>
+        <v>2193.216</v>
       </c>
       <c r="G33">
         <v>136.5</v>
@@ -3987,37 +3987,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M33">
-        <v>500.9990724</v>
+        <v>517.1603328</v>
       </c>
       <c r="N33">
-        <v>-412.4590724</v>
+        <v>-428.6203328</v>
       </c>
       <c r="O33">
-        <v>-102.86729265656</v>
+        <v>-106.89791100032</v>
       </c>
       <c r="P33">
-        <v>-309.59177974344</v>
+        <v>-321.72242179968</v>
       </c>
       <c r="Q33">
-        <v>-312.73177974344</v>
+        <v>-324.86242179968</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07841966470527273</v>
+        <v>0.07889936565682086</v>
       </c>
       <c r="T33">
-        <v>0.7533409862649593</v>
+        <v>0.7644195301806205</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04407568240439721</v>
+        <v>0.0426983173292598</v>
       </c>
       <c r="W33">
-        <v>0.2254069540890432</v>
+        <v>0.2257317367737605</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1767268741154659</v>
+        <v>0.1712041592993576</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1258857244142416</v>
+        <v>0.1277857244142416</v>
       </c>
       <c r="C34">
-        <v>-840.3802221579983</v>
+        <v>-937.1065195038029</v>
       </c>
       <c r="D34">
-        <v>1216.335777842002</v>
+        <v>1188.147480496197</v>
       </c>
       <c r="E34">
-        <v>-3517.384</v>
+        <v>-3448.846</v>
       </c>
       <c r="F34">
-        <v>2193.216</v>
+        <v>2261.754</v>
       </c>
       <c r="G34">
         <v>136.5</v>
@@ -4069,37 +4069,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M34">
-        <v>517.1603328</v>
+        <v>533.3215932000001</v>
       </c>
       <c r="N34">
-        <v>-428.6203328</v>
+        <v>-444.7815932</v>
       </c>
       <c r="O34">
-        <v>-106.89791100032</v>
+        <v>-110.92852934408</v>
       </c>
       <c r="P34">
-        <v>-321.72242179968</v>
+        <v>-333.85306385592</v>
       </c>
       <c r="Q34">
-        <v>-324.86242179968</v>
+        <v>-336.99306385592</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07889936565682086</v>
+        <v>0.07939338603975848</v>
       </c>
       <c r="T34">
-        <v>0.7644195301806205</v>
+        <v>0.7758287768997342</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.0426983173292598</v>
+        <v>0.04140442892534283</v>
       </c>
       <c r="W34">
-        <v>0.2257317367737605</v>
+        <v>0.2260368356594042</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1712041592993576</v>
+        <v>0.1660161544721044</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1277857244142416</v>
+        <v>0.1296857244142416</v>
       </c>
       <c r="C35">
-        <v>-937.1065195038029</v>
+        <v>-1032.555894814756</v>
       </c>
       <c r="D35">
-        <v>1188.147480496197</v>
+        <v>1161.236105185245</v>
       </c>
       <c r="E35">
-        <v>-3448.846</v>
+        <v>-3380.308</v>
       </c>
       <c r="F35">
-        <v>2261.754</v>
+        <v>2330.292</v>
       </c>
       <c r="G35">
         <v>136.5</v>
@@ -4151,37 +4151,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M35">
-        <v>533.3215932000001</v>
+        <v>549.4828536000001</v>
       </c>
       <c r="N35">
-        <v>-444.7815932</v>
+        <v>-460.9428536000001</v>
       </c>
       <c r="O35">
-        <v>-110.92852934408</v>
+        <v>-114.95914768784</v>
       </c>
       <c r="P35">
-        <v>-333.85306385592</v>
+        <v>-345.9837059121601</v>
       </c>
       <c r="Q35">
-        <v>-336.99306385592</v>
+        <v>-349.1237059121601</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07939338603975848</v>
+        <v>0.07990237673733058</v>
       </c>
       <c r="T35">
-        <v>0.7758287768997342</v>
+        <v>0.7875837583679119</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04140442892534283</v>
+        <v>0.04018665160400921</v>
       </c>
       <c r="W35">
-        <v>0.2260368356594042</v>
+        <v>0.2263239875517746</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1660161544721044</v>
+        <v>0.1611333263993954</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1296857244142416</v>
+        <v>0.1315857244142416</v>
       </c>
       <c r="C36">
-        <v>-1032.555894814756</v>
+        <v>-1126.813192692313</v>
       </c>
       <c r="D36">
-        <v>1161.236105185245</v>
+        <v>1135.516807307687</v>
       </c>
       <c r="E36">
-        <v>-3380.308</v>
+        <v>-3311.77</v>
       </c>
       <c r="F36">
-        <v>2330.292</v>
+        <v>2398.83</v>
       </c>
       <c r="G36">
         <v>136.5</v>
@@ -4233,37 +4233,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M36">
-        <v>549.4828536000001</v>
+        <v>565.6441140000001</v>
       </c>
       <c r="N36">
-        <v>-460.9428536000001</v>
+        <v>-477.104114</v>
       </c>
       <c r="O36">
-        <v>-114.95914768784</v>
+        <v>-118.9897660316</v>
       </c>
       <c r="P36">
-        <v>-345.9837059121601</v>
+        <v>-358.1143479684</v>
       </c>
       <c r="Q36">
-        <v>-349.1237059121601</v>
+        <v>-361.2543479684</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07990237673733058</v>
+        <v>0.08042702868713567</v>
       </c>
       <c r="T36">
-        <v>0.7875837583679119</v>
+        <v>0.7997004315735722</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04018665160400921</v>
+        <v>0.03903846155818038</v>
       </c>
       <c r="W36">
-        <v>0.2263239875517746</v>
+        <v>0.2265947307645811</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1611333263993954</v>
+        <v>0.1565295170736984</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1315857244142416</v>
+        <v>0.1334857244142416</v>
       </c>
       <c r="C37">
-        <v>-1126.813192692313</v>
+        <v>-1219.955903987077</v>
       </c>
       <c r="D37">
-        <v>1135.516807307687</v>
+        <v>1110.912096012923</v>
       </c>
       <c r="E37">
-        <v>-3311.77</v>
+        <v>-3243.232</v>
       </c>
       <c r="F37">
-        <v>2398.83</v>
+        <v>2467.368</v>
       </c>
       <c r="G37">
         <v>136.5</v>
@@ -4315,37 +4315,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M37">
-        <v>565.6441140000001</v>
+        <v>581.8053744000001</v>
       </c>
       <c r="N37">
-        <v>-477.104114</v>
+        <v>-493.2653744000001</v>
       </c>
       <c r="O37">
-        <v>-118.9897660316</v>
+        <v>-123.02038437536</v>
       </c>
       <c r="P37">
-        <v>-358.1143479684</v>
+        <v>-370.2449900246401</v>
       </c>
       <c r="Q37">
-        <v>-361.2543479684</v>
+        <v>-373.38499002464</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08042702868713567</v>
+        <v>0.08096807601037218</v>
       </c>
       <c r="T37">
-        <v>0.7997004315735722</v>
+        <v>0.8121957508169093</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03903846155818038</v>
+        <v>0.03795405984823092</v>
       </c>
       <c r="W37">
-        <v>0.2265947307645811</v>
+        <v>0.2268504326877872</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1565295170736984</v>
+        <v>0.1521814749327624</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1334857244142416</v>
+        <v>0.1353857244142416</v>
       </c>
       <c r="C38">
-        <v>-1219.955903987077</v>
+        <v>-1312.0549456176</v>
       </c>
       <c r="D38">
-        <v>1110.912096012923</v>
+        <v>1087.3510543824</v>
       </c>
       <c r="E38">
-        <v>-3243.232</v>
+        <v>-3174.694</v>
       </c>
       <c r="F38">
-        <v>2467.368</v>
+        <v>2535.906</v>
       </c>
       <c r="G38">
         <v>136.5</v>
@@ -4397,37 +4397,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M38">
-        <v>581.8053744</v>
+        <v>597.9666348000001</v>
       </c>
       <c r="N38">
-        <v>-493.2653744</v>
+        <v>-509.4266348</v>
       </c>
       <c r="O38">
-        <v>-123.02038437536</v>
+        <v>-127.05100271912</v>
       </c>
       <c r="P38">
-        <v>-370.24499002464</v>
+        <v>-382.37563208088</v>
       </c>
       <c r="Q38">
-        <v>-373.38499002464</v>
+        <v>-385.51563208088</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08096807601037216</v>
+        <v>0.08152629943910823</v>
       </c>
       <c r="T38">
-        <v>0.8121957508169092</v>
+        <v>0.8250877468616221</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03795405984823093</v>
+        <v>0.03692827444692738</v>
       </c>
       <c r="W38">
-        <v>0.2268504326877872</v>
+        <v>0.2270923128854145</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1521814749327624</v>
+        <v>0.1480684620967417</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1353857244142416</v>
+        <v>0.1372857244142416</v>
       </c>
       <c r="C39">
-        <v>-1312.0549456176</v>
+        <v>-1403.17534321629</v>
       </c>
       <c r="D39">
-        <v>1087.3510543824</v>
+        <v>1064.76865678371</v>
       </c>
       <c r="E39">
-        <v>-3174.694</v>
+        <v>-3106.156</v>
       </c>
       <c r="F39">
-        <v>2535.906</v>
+        <v>2604.444</v>
       </c>
       <c r="G39">
         <v>136.5</v>
@@ -4479,37 +4479,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M39">
-        <v>597.9666348000001</v>
+        <v>614.1278952</v>
       </c>
       <c r="N39">
-        <v>-509.4266348</v>
+        <v>-525.5878952</v>
       </c>
       <c r="O39">
-        <v>-127.05100271912</v>
+        <v>-131.08162106288</v>
       </c>
       <c r="P39">
-        <v>-382.37563208088</v>
+        <v>-394.50627413712</v>
       </c>
       <c r="Q39">
-        <v>-385.51563208088</v>
+        <v>-397.64627413712</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08152629943910823</v>
+        <v>0.08210253007522288</v>
       </c>
       <c r="T39">
-        <v>0.8250877468616221</v>
+        <v>0.838395613746487</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03692827444692738</v>
+        <v>0.03595647775095561</v>
       </c>
       <c r="W39">
-        <v>0.2270923128854145</v>
+        <v>0.2273214625463247</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1480684620967417</v>
+        <v>0.1441719236205116</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1372857244142416</v>
+        <v>0.1391857244142415</v>
       </c>
       <c r="C40">
-        <v>-1403.17534321629</v>
+        <v>-1493.376830441758</v>
       </c>
       <c r="D40">
-        <v>1064.76865678371</v>
+        <v>1043.105169558242</v>
       </c>
       <c r="E40">
-        <v>-3106.156</v>
+        <v>-3037.618</v>
       </c>
       <c r="F40">
-        <v>2604.444</v>
+        <v>2672.982</v>
       </c>
       <c r="G40">
         <v>136.5</v>
@@ -4561,37 +4561,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M40">
-        <v>614.1278952</v>
+        <v>630.2891556000001</v>
       </c>
       <c r="N40">
-        <v>-525.5878952</v>
+        <v>-541.7491556000001</v>
       </c>
       <c r="O40">
-        <v>-131.08162106288</v>
+        <v>-135.11223940664</v>
       </c>
       <c r="P40">
-        <v>-394.50627413712</v>
+        <v>-406.6369161933601</v>
       </c>
       <c r="Q40">
-        <v>-397.64627413712</v>
+        <v>-409.7769161933601</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08210253007522288</v>
+        <v>0.08269765351907898</v>
       </c>
       <c r="T40">
-        <v>0.838395613746487</v>
+        <v>0.8521398041357735</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03595647775095561</v>
+        <v>0.0350345167829824</v>
       </c>
       <c r="W40">
-        <v>0.2273214625463247</v>
+        <v>0.2275388609425728</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1441719236205116</v>
+        <v>0.1404752076302421</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1391857244142415</v>
+        <v>0.1410857244142416</v>
       </c>
       <c r="C41">
-        <v>-1493.376830441758</v>
+        <v>-1582.71437658935</v>
       </c>
       <c r="D41">
-        <v>1043.105169558242</v>
+        <v>1022.305623410651</v>
       </c>
       <c r="E41">
-        <v>-3037.618</v>
+        <v>-2969.08</v>
       </c>
       <c r="F41">
-        <v>2672.982</v>
+        <v>2741.52</v>
       </c>
       <c r="G41">
         <v>136.5</v>
@@ -4643,37 +4643,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M41">
-        <v>630.2891556000001</v>
+        <v>646.4504160000001</v>
       </c>
       <c r="N41">
-        <v>-541.7491556000001</v>
+        <v>-557.9104160000002</v>
       </c>
       <c r="O41">
-        <v>-135.11223940664</v>
+        <v>-139.1428577504001</v>
       </c>
       <c r="P41">
-        <v>-406.6369161933601</v>
+        <v>-418.7675582496001</v>
       </c>
       <c r="Q41">
-        <v>-409.7769161933601</v>
+        <v>-421.9075582496001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08269765351907898</v>
+        <v>0.08331261441106363</v>
       </c>
       <c r="T41">
-        <v>0.8521398041357735</v>
+        <v>0.8663421342047032</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0350345167829824</v>
+        <v>0.03415865386340783</v>
       </c>
       <c r="W41">
-        <v>0.2275388609425728</v>
+        <v>0.2277453894190085</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1404752076302421</v>
+        <v>0.136963327439486</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1410857244142416</v>
+        <v>0.1429857244142416</v>
       </c>
       <c r="C42">
-        <v>-1582.71437658935</v>
+        <v>-1671.238652312326</v>
       </c>
       <c r="D42">
-        <v>1022.305623410651</v>
+        <v>1002.319347687674</v>
       </c>
       <c r="E42">
-        <v>-2969.08</v>
+        <v>-2900.542</v>
       </c>
       <c r="F42">
-        <v>2741.52</v>
+        <v>2810.058</v>
       </c>
       <c r="G42">
         <v>136.5</v>
@@ -4725,37 +4725,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M42">
-        <v>646.4504160000001</v>
+        <v>662.6116764000001</v>
       </c>
       <c r="N42">
-        <v>-557.9104160000002</v>
+        <v>-574.0716764000001</v>
       </c>
       <c r="O42">
-        <v>-139.1428577504001</v>
+        <v>-143.17347609416</v>
       </c>
       <c r="P42">
-        <v>-418.7675582496001</v>
+        <v>-430.8982003058401</v>
       </c>
       <c r="Q42">
-        <v>-421.9075582496001</v>
+        <v>-434.0382003058401</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08331261441106363</v>
+        <v>0.08394842143497996</v>
       </c>
       <c r="T42">
-        <v>0.8663421342047032</v>
+        <v>0.8810258991912235</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03415865386340783</v>
+        <v>0.03332551596430032</v>
       </c>
       <c r="W42">
-        <v>0.2277453894190085</v>
+        <v>0.227941843335618</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.136963327439486</v>
+        <v>0.1336227584775473</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1429857244142416</v>
+        <v>0.1448857244142416</v>
       </c>
       <c r="C43">
-        <v>-1671.238652312326</v>
+        <v>-1758.996441760955</v>
       </c>
       <c r="D43">
-        <v>1002.319347687674</v>
+        <v>983.0995582390456</v>
       </c>
       <c r="E43">
-        <v>-2900.542</v>
+        <v>-2832.004</v>
       </c>
       <c r="F43">
-        <v>2810.058</v>
+        <v>2878.596</v>
       </c>
       <c r="G43">
         <v>136.5</v>
@@ -4807,37 +4807,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M43">
-        <v>662.6116764000001</v>
+        <v>678.7729368000001</v>
       </c>
       <c r="N43">
-        <v>-574.0716764000001</v>
+        <v>-590.2329368000002</v>
       </c>
       <c r="O43">
-        <v>-143.17347609416</v>
+        <v>-147.20409443792</v>
       </c>
       <c r="P43">
-        <v>-430.8982003058401</v>
+        <v>-443.0288423620801</v>
       </c>
       <c r="Q43">
-        <v>-434.0382003058401</v>
+        <v>-446.1688423620801</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08394842143497996</v>
+        <v>0.08460615283903136</v>
       </c>
       <c r="T43">
-        <v>0.8810258991912235</v>
+        <v>0.8962160009014172</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03332551596430032</v>
+        <v>0.03253205129848365</v>
       </c>
       <c r="W43">
-        <v>0.227941843335618</v>
+        <v>0.2281289423038176</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1336227584775473</v>
+        <v>0.1304412642280819</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1448857244142416</v>
+        <v>0.1467857244142416</v>
       </c>
       <c r="C44">
-        <v>-1758.996441760954</v>
+        <v>-1846.031008196346</v>
       </c>
       <c r="D44">
-        <v>983.0995582390456</v>
+        <v>964.6029918036538</v>
       </c>
       <c r="E44">
-        <v>-2832.004</v>
+        <v>-2763.466</v>
       </c>
       <c r="F44">
-        <v>2878.596</v>
+        <v>2947.134</v>
       </c>
       <c r="G44">
         <v>136.5</v>
@@ -4889,37 +4889,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M44">
-        <v>678.7729368</v>
+        <v>694.9341972000001</v>
       </c>
       <c r="N44">
-        <v>-590.2329368000001</v>
+        <v>-606.3941972000001</v>
       </c>
       <c r="O44">
-        <v>-147.20409443792</v>
+        <v>-151.23471278168</v>
       </c>
       <c r="P44">
-        <v>-443.02884236208</v>
+        <v>-455.1594844183201</v>
       </c>
       <c r="Q44">
-        <v>-446.16884236208</v>
+        <v>-458.29948441832</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08460615283903135</v>
+        <v>0.08528696253796172</v>
       </c>
       <c r="T44">
-        <v>0.896216000901417</v>
+        <v>0.9119390886365296</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03253205129848365</v>
+        <v>0.03177549196596077</v>
       </c>
       <c r="W44">
-        <v>0.2281289423038176</v>
+        <v>0.2283073389944265</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1304412642280819</v>
+        <v>0.1274077464553358</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1467857244142416</v>
+        <v>0.1486857244142416</v>
       </c>
       <c r="C45">
-        <v>-1846.031008196346</v>
+        <v>-1932.382419093352</v>
       </c>
       <c r="D45">
-        <v>964.6029918036538</v>
+        <v>946.7895809066481</v>
       </c>
       <c r="E45">
-        <v>-2763.466</v>
+        <v>-2694.928</v>
       </c>
       <c r="F45">
-        <v>2947.134</v>
+        <v>3015.672</v>
       </c>
       <c r="G45">
         <v>136.5</v>
@@ -4971,37 +4971,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M45">
-        <v>694.9341972000001</v>
+        <v>711.0954576</v>
       </c>
       <c r="N45">
-        <v>-606.3941972000001</v>
+        <v>-622.5554576000001</v>
       </c>
       <c r="O45">
-        <v>-151.23471278168</v>
+        <v>-155.26533112544</v>
       </c>
       <c r="P45">
-        <v>-455.1594844183201</v>
+        <v>-467.2901264745601</v>
       </c>
       <c r="Q45">
-        <v>-458.29948441832</v>
+        <v>-470.43012647456</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08528696253796172</v>
+        <v>0.08599208686899676</v>
       </c>
       <c r="T45">
-        <v>0.9119390886365296</v>
+        <v>0.9282237152193248</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03177549196596077</v>
+        <v>0.03105332169400712</v>
       </c>
       <c r="W45">
-        <v>0.2283073389944265</v>
+        <v>0.2284776267445531</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1274077464553358</v>
+        <v>0.1245121158540782</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1486857244142416</v>
+        <v>0.1505857244142416</v>
       </c>
       <c r="C46">
-        <v>-1932.382419093352</v>
+        <v>-2018.087835874393</v>
       </c>
       <c r="D46">
-        <v>946.7895809066481</v>
+        <v>929.622164125607</v>
       </c>
       <c r="E46">
-        <v>-2694.928</v>
+        <v>-2626.39</v>
       </c>
       <c r="F46">
-        <v>3015.672</v>
+        <v>3084.21</v>
       </c>
       <c r="G46">
         <v>136.5</v>
@@ -5053,37 +5053,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M46">
-        <v>711.0954576</v>
+        <v>727.2567180000001</v>
       </c>
       <c r="N46">
-        <v>-622.5554576000001</v>
+        <v>-638.7167180000001</v>
       </c>
       <c r="O46">
-        <v>-155.26533112544</v>
+        <v>-159.2959494692</v>
       </c>
       <c r="P46">
-        <v>-467.2901264745601</v>
+        <v>-479.4207685308001</v>
       </c>
       <c r="Q46">
-        <v>-470.43012647456</v>
+        <v>-482.5607685308001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08599208686899676</v>
+        <v>0.08672285208479669</v>
       </c>
       <c r="T46">
-        <v>0.9282237152193248</v>
+        <v>0.9451005100414943</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03105332169400712</v>
+        <v>0.03036324787858474</v>
       </c>
       <c r="W46">
-        <v>0.2284776267445531</v>
+        <v>0.2286403461502297</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1245121158540782</v>
+        <v>0.1217451799462098</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1505857244142416</v>
+        <v>0.1524857244142416</v>
       </c>
       <c r="C47">
-        <v>-2018.087835874393</v>
+        <v>-2103.181772683525</v>
       </c>
       <c r="D47">
-        <v>929.622164125607</v>
+        <v>913.0662273164747</v>
       </c>
       <c r="E47">
-        <v>-2626.39</v>
+        <v>-2557.852</v>
       </c>
       <c r="F47">
-        <v>3084.21</v>
+        <v>3152.748</v>
       </c>
       <c r="G47">
         <v>136.5</v>
@@ -5135,37 +5135,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M47">
-        <v>727.2567180000001</v>
+        <v>743.4179784</v>
       </c>
       <c r="N47">
-        <v>-638.7167180000001</v>
+        <v>-654.8779784000001</v>
       </c>
       <c r="O47">
-        <v>-159.2959494692</v>
+        <v>-163.32656781296</v>
       </c>
       <c r="P47">
-        <v>-479.4207685308001</v>
+        <v>-491.55141058704</v>
       </c>
       <c r="Q47">
-        <v>-482.5607685308001</v>
+        <v>-494.69141058704</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08672285208479669</v>
+        <v>0.0874806826789596</v>
       </c>
       <c r="T47">
-        <v>0.9451005100414943</v>
+        <v>0.9626023713385591</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03036324787858474</v>
+        <v>0.02970317727252855</v>
       </c>
       <c r="W47">
-        <v>0.2286403461502297</v>
+        <v>0.2287959907991378</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1217451799462098</v>
+        <v>0.119098545599553</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1524857244142416</v>
+        <v>0.1543857244142416</v>
       </c>
       <c r="C48">
-        <v>-2103.181772683525</v>
+        <v>-2187.696327992796</v>
       </c>
       <c r="D48">
-        <v>913.0662273164747</v>
+        <v>897.0896720072043</v>
       </c>
       <c r="E48">
-        <v>-2557.852</v>
+        <v>-2489.314</v>
       </c>
       <c r="F48">
-        <v>3152.748</v>
+        <v>3221.286</v>
       </c>
       <c r="G48">
         <v>136.5</v>
@@ -5217,37 +5217,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M48">
-        <v>743.4179784</v>
+        <v>759.5792388000001</v>
       </c>
       <c r="N48">
-        <v>-654.8779784000001</v>
+        <v>-671.0392388000001</v>
       </c>
       <c r="O48">
-        <v>-163.32656781296</v>
+        <v>-167.35718615672</v>
       </c>
       <c r="P48">
-        <v>-491.55141058704</v>
+        <v>-503.6820526432801</v>
       </c>
       <c r="Q48">
-        <v>-494.69141058704</v>
+        <v>-506.8220526432801</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0874806826789596</v>
+        <v>0.08826711065403431</v>
       </c>
       <c r="T48">
-        <v>0.9626023713385591</v>
+        <v>0.9807646802317395</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02970317727252855</v>
+        <v>0.02907119477736837</v>
       </c>
       <c r="W48">
-        <v>0.2287959907991378</v>
+        <v>0.2289450122714966</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.119098545599553</v>
+        <v>0.1165645339910519</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1543857244142416</v>
+        <v>0.1562857244142416</v>
       </c>
       <c r="C49">
-        <v>-2187.696327992796</v>
+        <v>-2271.661392311288</v>
       </c>
       <c r="D49">
-        <v>897.0896720072043</v>
+        <v>881.6626076887125</v>
       </c>
       <c r="E49">
-        <v>-2489.314</v>
+        <v>-2420.776</v>
       </c>
       <c r="F49">
-        <v>3221.286</v>
+        <v>3289.824000000001</v>
       </c>
       <c r="G49">
         <v>136.5</v>
@@ -5299,37 +5299,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M49">
-        <v>759.5792388000001</v>
+        <v>775.7404992000002</v>
       </c>
       <c r="N49">
-        <v>-671.0392388000001</v>
+        <v>-687.2004992000002</v>
       </c>
       <c r="O49">
-        <v>-167.35718615672</v>
+        <v>-171.3878045004801</v>
       </c>
       <c r="P49">
-        <v>-503.6820526432801</v>
+        <v>-515.8126946995201</v>
       </c>
       <c r="Q49">
-        <v>-506.8220526432801</v>
+        <v>-518.9526946995201</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08826711065403431</v>
+        <v>0.08908378585891959</v>
       </c>
       <c r="T49">
-        <v>0.9807646802317395</v>
+        <v>0.9996255394669652</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02907119477736837</v>
+        <v>0.02846554488617319</v>
       </c>
       <c r="W49">
-        <v>0.2289450122714966</v>
+        <v>0.2290878245158404</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1165645339910519</v>
+        <v>0.1141361061995717</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1562857244142416</v>
+        <v>0.1581857244142416</v>
       </c>
       <c r="C50">
-        <v>-2271.661392311288</v>
+        <v>-2355.104834824912</v>
       </c>
       <c r="D50">
-        <v>881.6626076887125</v>
+        <v>866.7571651750881</v>
       </c>
       <c r="E50">
-        <v>-2420.776</v>
+        <v>-2352.238</v>
       </c>
       <c r="F50">
-        <v>3289.824</v>
+        <v>3358.362</v>
       </c>
       <c r="G50">
         <v>136.5</v>
@@ -5381,37 +5381,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M50">
-        <v>775.7404992</v>
+        <v>791.9017596000001</v>
       </c>
       <c r="N50">
-        <v>-687.2004992000001</v>
+        <v>-703.3617596000001</v>
       </c>
       <c r="O50">
-        <v>-171.38780450048</v>
+        <v>-175.41842284424</v>
       </c>
       <c r="P50">
-        <v>-515.8126946995201</v>
+        <v>-527.9433367557601</v>
       </c>
       <c r="Q50">
-        <v>-518.9526946995201</v>
+        <v>-531.0833367557601</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08908378585891959</v>
+        <v>0.0899324875424278</v>
       </c>
       <c r="T50">
-        <v>0.9996255394669652</v>
+        <v>1.019226040240827</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0284655448861732</v>
+        <v>0.02788461539870027</v>
       </c>
       <c r="W50">
-        <v>0.2290878245158404</v>
+        <v>0.2292248076889865</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1141361061995717</v>
+        <v>0.1118067979097845</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1581857244142416</v>
+        <v>0.1600857244142416</v>
       </c>
       <c r="C51">
-        <v>-2355.104834824912</v>
+        <v>-2438.052671418882</v>
       </c>
       <c r="D51">
-        <v>866.7571651750881</v>
+        <v>852.3473285811181</v>
       </c>
       <c r="E51">
-        <v>-2352.238</v>
+        <v>-2283.7</v>
       </c>
       <c r="F51">
-        <v>3358.362</v>
+        <v>3426.9</v>
       </c>
       <c r="G51">
         <v>136.5</v>
@@ -5463,37 +5463,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M51">
-        <v>791.9017596000001</v>
+        <v>808.0630200000001</v>
       </c>
       <c r="N51">
-        <v>-703.3617596000001</v>
+        <v>-719.5230200000001</v>
       </c>
       <c r="O51">
-        <v>-175.41842284424</v>
+        <v>-179.449041188</v>
       </c>
       <c r="P51">
-        <v>-527.9433367557601</v>
+        <v>-540.0739788120001</v>
       </c>
       <c r="Q51">
-        <v>-531.0833367557601</v>
+        <v>-543.2139788120001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0899324875424278</v>
+        <v>0.09081513729327637</v>
       </c>
       <c r="T51">
-        <v>1.019226040240827</v>
+        <v>1.039610561045644</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02788461539870027</v>
+        <v>0.02732692309072627</v>
       </c>
       <c r="W51">
-        <v>0.2292248076889865</v>
+        <v>0.2293563115352067</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1118067979097845</v>
+        <v>0.1095706619515888</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1600857244142416</v>
+        <v>0.1619857244142416</v>
       </c>
       <c r="C52">
-        <v>-2438.052671418882</v>
+        <v>-2520.529216214025</v>
       </c>
       <c r="D52">
-        <v>852.3473285811181</v>
+        <v>838.4087837859749</v>
       </c>
       <c r="E52">
-        <v>-2283.7</v>
+        <v>-2215.162</v>
       </c>
       <c r="F52">
-        <v>3426.9</v>
+        <v>3495.438</v>
       </c>
       <c r="G52">
         <v>136.5</v>
@@ -5545,37 +5545,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M52">
-        <v>808.0630200000001</v>
+        <v>824.2242804000001</v>
       </c>
       <c r="N52">
-        <v>-719.5230200000001</v>
+        <v>-735.6842804000001</v>
       </c>
       <c r="O52">
-        <v>-179.449041188</v>
+        <v>-183.47965953176</v>
       </c>
       <c r="P52">
-        <v>-540.0739788120001</v>
+        <v>-552.2046208682401</v>
       </c>
       <c r="Q52">
-        <v>-543.2139788120001</v>
+        <v>-555.3446208682401</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09081513729327637</v>
+        <v>0.09173381356456772</v>
       </c>
       <c r="T52">
-        <v>1.039610561045644</v>
+        <v>1.0608271031078</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02732692309072627</v>
+        <v>0.02679110106933948</v>
       </c>
       <c r="W52">
-        <v>0.2293563115352067</v>
+        <v>0.2294826583678498</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1095706619515888</v>
+        <v>0.1074222175995969</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1619857244142416</v>
+        <v>0.1638857244142416</v>
       </c>
       <c r="C53">
-        <v>-2520.529216214025</v>
+        <v>-2602.557218473784</v>
       </c>
       <c r="D53">
-        <v>838.4087837859749</v>
+        <v>824.9187815262161</v>
       </c>
       <c r="E53">
-        <v>-2215.162</v>
+        <v>-2146.624</v>
       </c>
       <c r="F53">
-        <v>3495.438</v>
+        <v>3563.976</v>
       </c>
       <c r="G53">
         <v>136.5</v>
@@ -5627,37 +5627,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M53">
-        <v>824.2242804000001</v>
+        <v>840.3855408000001</v>
       </c>
       <c r="N53">
-        <v>-735.6842804000001</v>
+        <v>-751.8455408000001</v>
       </c>
       <c r="O53">
-        <v>-183.47965953176</v>
+        <v>-187.51027787552</v>
       </c>
       <c r="P53">
-        <v>-552.2046208682401</v>
+        <v>-564.33526292448</v>
       </c>
       <c r="Q53">
-        <v>-555.3446208682401</v>
+        <v>-567.47526292448</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09173381356456772</v>
+        <v>0.09269076801382956</v>
       </c>
       <c r="T53">
-        <v>1.0608271031078</v>
+        <v>1.082927667755879</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02679110106933948</v>
+        <v>0.0262758875872368</v>
       </c>
       <c r="W53">
-        <v>0.2294826583678498</v>
+        <v>0.2296041457069296</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1074222175995969</v>
+        <v>0.1053564057226816</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1638857244142416</v>
+        <v>0.1657857244142416</v>
       </c>
       <c r="C54">
-        <v>-2602.557218473784</v>
+        <v>-2684.157986503493</v>
       </c>
       <c r="D54">
-        <v>824.9187815262161</v>
+        <v>811.8560134965073</v>
       </c>
       <c r="E54">
-        <v>-2146.624</v>
+        <v>-2078.086</v>
       </c>
       <c r="F54">
-        <v>3563.976</v>
+        <v>3632.514</v>
       </c>
       <c r="G54">
         <v>136.5</v>
@@ -5709,37 +5709,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M54">
-        <v>840.3855408000001</v>
+        <v>856.5468012000001</v>
       </c>
       <c r="N54">
-        <v>-751.8455408000001</v>
+        <v>-768.0068012000002</v>
       </c>
       <c r="O54">
-        <v>-187.51027787552</v>
+        <v>-191.5408962192801</v>
       </c>
       <c r="P54">
-        <v>-564.33526292448</v>
+        <v>-576.4659049807201</v>
       </c>
       <c r="Q54">
-        <v>-567.47526292448</v>
+        <v>-579.6059049807201</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09269076801382956</v>
+        <v>0.09368844392901741</v>
       </c>
       <c r="T54">
-        <v>1.082927667755879</v>
+        <v>1.105968681963451</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0262758875872368</v>
+        <v>0.02578011612332667</v>
       </c>
       <c r="W54">
-        <v>0.2296041457069296</v>
+        <v>0.2297210486181196</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1053564057226816</v>
+        <v>0.1033685490109328</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1657857244142416</v>
+        <v>0.1676857244142416</v>
       </c>
       <c r="C55">
-        <v>-2684.157986503493</v>
+        <v>-2765.351499961336</v>
       </c>
       <c r="D55">
-        <v>811.8560134965073</v>
+        <v>799.2005000386642</v>
       </c>
       <c r="E55">
-        <v>-2078.086</v>
+        <v>-2009.548</v>
       </c>
       <c r="F55">
-        <v>3632.514</v>
+        <v>3701.052</v>
       </c>
       <c r="G55">
         <v>136.5</v>
@@ -5791,37 +5791,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M55">
-        <v>856.5468012000001</v>
+        <v>872.7080616000001</v>
       </c>
       <c r="N55">
-        <v>-768.0068012000002</v>
+        <v>-784.1680616000001</v>
       </c>
       <c r="O55">
-        <v>-191.5408962192801</v>
+        <v>-195.57151456304</v>
       </c>
       <c r="P55">
-        <v>-576.4659049807201</v>
+        <v>-588.59654703696</v>
       </c>
       <c r="Q55">
-        <v>-579.6059049807201</v>
+        <v>-591.73654703696</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09368844392901741</v>
+        <v>0.09472949705790909</v>
       </c>
       <c r="T55">
-        <v>1.105968681963451</v>
+        <v>1.130011479397439</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02578011612332667</v>
+        <v>0.02530270656548728</v>
       </c>
       <c r="W55">
-        <v>0.2297210486181196</v>
+        <v>0.2298336217918581</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1033685490109328</v>
+        <v>0.1014543166218415</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1676857244142416</v>
+        <v>0.1695857244142416</v>
       </c>
       <c r="C56">
-        <v>-2765.351499961336</v>
+        <v>-2846.156511826065</v>
       </c>
       <c r="D56">
-        <v>799.2005000386642</v>
+        <v>786.9334881739359</v>
       </c>
       <c r="E56">
-        <v>-2009.548</v>
+        <v>-1941.01</v>
       </c>
       <c r="F56">
-        <v>3701.052</v>
+        <v>3769.590000000001</v>
       </c>
       <c r="G56">
         <v>136.5</v>
@@ -5873,37 +5873,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M56">
-        <v>872.7080616000001</v>
+        <v>888.8693220000001</v>
       </c>
       <c r="N56">
-        <v>-784.1680616000001</v>
+        <v>-800.3293220000002</v>
       </c>
       <c r="O56">
-        <v>-195.57151456304</v>
+        <v>-199.6021329068001</v>
       </c>
       <c r="P56">
-        <v>-588.59654703696</v>
+        <v>-600.7271890932001</v>
       </c>
       <c r="Q56">
-        <v>-591.73654703696</v>
+        <v>-603.8671890932001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09472949705790909</v>
+        <v>0.09581681921475152</v>
       </c>
       <c r="T56">
-        <v>1.130011479397439</v>
+        <v>1.155122845606271</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02530270656548728</v>
+        <v>0.0248426573552057</v>
       </c>
       <c r="W56">
-        <v>0.2298336217918581</v>
+        <v>0.2299421013956425</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1014543166218415</v>
+        <v>0.09960969268326259</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1695857244142416</v>
+        <v>0.1714857244142416</v>
       </c>
       <c r="C57">
-        <v>-2846.156511826065</v>
+        <v>-2926.590641115996</v>
       </c>
       <c r="D57">
-        <v>786.9334881739359</v>
+        <v>775.0373588840047</v>
       </c>
       <c r="E57">
-        <v>-1941.01</v>
+        <v>-1872.472</v>
       </c>
       <c r="F57">
-        <v>3769.590000000001</v>
+        <v>3838.128000000001</v>
       </c>
       <c r="G57">
         <v>136.5</v>
@@ -5955,37 +5955,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M57">
-        <v>888.8693220000001</v>
+        <v>905.0305824000002</v>
       </c>
       <c r="N57">
-        <v>-800.3293220000002</v>
+        <v>-816.4905824000002</v>
       </c>
       <c r="O57">
-        <v>-199.6021329068001</v>
+        <v>-203.6327512505601</v>
       </c>
       <c r="P57">
-        <v>-600.7271890932001</v>
+        <v>-612.8578311494401</v>
       </c>
       <c r="Q57">
-        <v>-603.8671890932001</v>
+        <v>-615.9978311494401</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09581681921475152</v>
+        <v>0.09695356510599587</v>
       </c>
       <c r="T57">
-        <v>1.155122845606271</v>
+        <v>1.181375637551868</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.0248426573552057</v>
+        <v>0.02439903847386274</v>
       </c>
       <c r="W57">
-        <v>0.2299421013956425</v>
+        <v>0.2300467067278632</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.09960969268326259</v>
+        <v>0.09783094817106142</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1714857244142416</v>
+        <v>0.1733857244142416</v>
       </c>
       <c r="C58">
-        <v>-2926.590641115996</v>
+        <v>-3006.670457323415</v>
       </c>
       <c r="D58">
-        <v>775.0373588840047</v>
+        <v>763.4955426765857</v>
       </c>
       <c r="E58">
-        <v>-1872.472</v>
+        <v>-1803.934</v>
       </c>
       <c r="F58">
-        <v>3838.128000000001</v>
+        <v>3906.666000000001</v>
       </c>
       <c r="G58">
         <v>136.5</v>
@@ -6037,37 +6037,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M58">
-        <v>905.0305824000002</v>
+        <v>921.1918428000001</v>
       </c>
       <c r="N58">
-        <v>-816.4905824000002</v>
+        <v>-832.6518428000002</v>
       </c>
       <c r="O58">
-        <v>-203.6327512505601</v>
+        <v>-207.66336959432</v>
       </c>
       <c r="P58">
-        <v>-612.8578311494401</v>
+        <v>-624.9884732056801</v>
       </c>
       <c r="Q58">
-        <v>-615.9978311494401</v>
+        <v>-628.1284732056801</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09695356510599587</v>
+        <v>0.09814318289915858</v>
       </c>
       <c r="T58">
-        <v>1.181375637551868</v>
+        <v>1.208849489587958</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02439903847386274</v>
+        <v>0.02397098516730374</v>
       </c>
       <c r="W58">
-        <v>0.2300467067278632</v>
+        <v>0.2301476416975498</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.09783094817106142</v>
+        <v>0.09611461574700775</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1733857244142416</v>
+        <v>0.1752857244142416</v>
       </c>
       <c r="C59">
-        <v>-3006.670457323415</v>
+        <v>-3086.411557415319</v>
       </c>
       <c r="D59">
-        <v>763.4955426765857</v>
+        <v>752.2924425846812</v>
       </c>
       <c r="E59">
-        <v>-1803.934</v>
+        <v>-1735.396</v>
       </c>
       <c r="F59">
-        <v>3906.666000000001</v>
+        <v>3975.204000000001</v>
       </c>
       <c r="G59">
         <v>136.5</v>
@@ -6119,37 +6119,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M59">
-        <v>921.1918428000001</v>
+        <v>937.3531032000002</v>
       </c>
       <c r="N59">
-        <v>-832.6518428000002</v>
+        <v>-848.8131032000002</v>
       </c>
       <c r="O59">
-        <v>-207.66336959432</v>
+        <v>-211.6939879380801</v>
       </c>
       <c r="P59">
-        <v>-624.9884732056801</v>
+        <v>-637.1191152619201</v>
       </c>
       <c r="Q59">
-        <v>-628.1284732056801</v>
+        <v>-640.2591152619201</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09814318289915858</v>
+        <v>0.09938944915866235</v>
       </c>
       <c r="T59">
-        <v>1.208849489587958</v>
+        <v>1.237631620292433</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02397098516730374</v>
+        <v>0.0235576923195916</v>
       </c>
       <c r="W59">
-        <v>0.2301476416975498</v>
+        <v>0.2302450961510403</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.09611461574700775</v>
+        <v>0.09445746719964554</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1752857244142416</v>
+        <v>0.1771857244142415</v>
       </c>
       <c r="C60">
-        <v>-3086.411557415318</v>
+        <v>-3165.828636153007</v>
       </c>
       <c r="D60">
-        <v>752.2924425846812</v>
+        <v>741.4133638469923</v>
       </c>
       <c r="E60">
-        <v>-1735.396000000001</v>
+        <v>-1666.858000000001</v>
       </c>
       <c r="F60">
-        <v>3975.204</v>
+        <v>4043.742</v>
       </c>
       <c r="G60">
         <v>136.5</v>
@@ -6201,37 +6201,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M60">
-        <v>937.3531032</v>
+        <v>953.5143636</v>
       </c>
       <c r="N60">
-        <v>-848.8131032</v>
+        <v>-864.9743636000001</v>
       </c>
       <c r="O60">
-        <v>-211.69398793808</v>
+        <v>-215.72460628184</v>
       </c>
       <c r="P60">
-        <v>-637.11911526192</v>
+        <v>-649.2497573181601</v>
       </c>
       <c r="Q60">
-        <v>-640.25911526192</v>
+        <v>-652.38975731816</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09938944915866232</v>
+        <v>0.1006965088942395</v>
       </c>
       <c r="T60">
-        <v>1.237631620292433</v>
+        <v>1.267817757372736</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02355769231959161</v>
+        <v>0.02315840939892056</v>
       </c>
       <c r="W60">
-        <v>0.2302450961510403</v>
+        <v>0.2303392470637345</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09445746719964554</v>
+        <v>0.09285649317931255</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1771857244142415</v>
+        <v>0.1790857244142415</v>
       </c>
       <c r="C61">
-        <v>-3165.828636153007</v>
+        <v>-3244.935550397201</v>
       </c>
       <c r="D61">
-        <v>741.4133638469923</v>
+        <v>730.844449602799</v>
       </c>
       <c r="E61">
-        <v>-1666.858000000001</v>
+        <v>-1598.320000000001</v>
       </c>
       <c r="F61">
-        <v>4043.742</v>
+        <v>4112.28</v>
       </c>
       <c r="G61">
         <v>136.5</v>
@@ -6283,37 +6283,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M61">
-        <v>953.5143636</v>
+        <v>969.675624</v>
       </c>
       <c r="N61">
-        <v>-864.9743636000001</v>
+        <v>-881.135624</v>
       </c>
       <c r="O61">
-        <v>-215.72460628184</v>
+        <v>-219.7552246256</v>
       </c>
       <c r="P61">
-        <v>-649.2497573181601</v>
+        <v>-661.3803993744</v>
       </c>
       <c r="Q61">
-        <v>-652.38975731816</v>
+        <v>-664.5203993744</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1006965088942395</v>
+        <v>0.1020689216165954</v>
       </c>
       <c r="T61">
-        <v>1.267817757372736</v>
+        <v>1.299513201307055</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02315840939892056</v>
+        <v>0.02277243590893856</v>
       </c>
       <c r="W61">
-        <v>0.2303392470637345</v>
+        <v>0.2304302596126723</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09285649317931255</v>
+        <v>0.09130888495965739</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1790857244142415</v>
+        <v>0.1809857244142415</v>
       </c>
       <c r="C62">
-        <v>-3244.935550397201</v>
+        <v>-3323.745377990404</v>
       </c>
       <c r="D62">
-        <v>730.844449602799</v>
+        <v>720.5726220095958</v>
       </c>
       <c r="E62">
-        <v>-1598.320000000001</v>
+        <v>-1529.782</v>
       </c>
       <c r="F62">
-        <v>4112.28</v>
+        <v>4180.818</v>
       </c>
       <c r="G62">
         <v>136.5</v>
@@ -6365,37 +6365,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M62">
-        <v>969.675624</v>
+        <v>985.8368844000001</v>
       </c>
       <c r="N62">
-        <v>-881.135624</v>
+        <v>-897.2968844000002</v>
       </c>
       <c r="O62">
-        <v>-219.7552246256</v>
+        <v>-223.7858429693601</v>
       </c>
       <c r="P62">
-        <v>-661.3803993744</v>
+        <v>-673.5110414306401</v>
       </c>
       <c r="Q62">
-        <v>-664.5203993744</v>
+        <v>-676.6510414306401</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1020689216165954</v>
+        <v>0.1035117144785594</v>
       </c>
       <c r="T62">
-        <v>1.299513201307055</v>
+        <v>1.33283405262262</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02277243590893856</v>
+        <v>0.02239911728748055</v>
       </c>
       <c r="W62">
-        <v>0.2304302596126723</v>
+        <v>0.2305182881436121</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09130888495965739</v>
+        <v>0.08981201799310556</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1809857244142415</v>
+        <v>0.1828857244142416</v>
       </c>
       <c r="C63">
-        <v>-3323.745377990404</v>
+        <v>-3402.27047174264</v>
       </c>
       <c r="D63">
-        <v>720.5726220095958</v>
+        <v>710.5855282573599</v>
       </c>
       <c r="E63">
-        <v>-1529.782</v>
+        <v>-1461.244000000001</v>
       </c>
       <c r="F63">
-        <v>4180.818</v>
+        <v>4249.356</v>
       </c>
       <c r="G63">
         <v>136.5</v>
@@ -6447,37 +6447,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M63">
-        <v>985.8368844000001</v>
+        <v>1001.9981448</v>
       </c>
       <c r="N63">
-        <v>-897.2968844000002</v>
+        <v>-913.4581448</v>
       </c>
       <c r="O63">
-        <v>-223.7858429693601</v>
+        <v>-227.81646131312</v>
       </c>
       <c r="P63">
-        <v>-673.5110414306401</v>
+        <v>-685.64168348688</v>
       </c>
       <c r="Q63">
-        <v>-676.6510414306401</v>
+        <v>-688.78168348688</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1035117144785594</v>
+        <v>0.1050304438069426</v>
       </c>
       <c r="T63">
-        <v>1.33283405262262</v>
+        <v>1.367908632954794</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02239911728748055</v>
+        <v>0.0220378412021986</v>
       </c>
       <c r="W63">
-        <v>0.2305182881436121</v>
+        <v>0.2306034770445216</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.08981201799310556</v>
+        <v>0.08836343705773297</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1828857244142416</v>
+        <v>0.1847857244142415</v>
       </c>
       <c r="C64">
-        <v>-3402.27047174264</v>
+        <v>-3480.522508989121</v>
       </c>
       <c r="D64">
-        <v>710.5855282573599</v>
+        <v>700.8714910108798</v>
       </c>
       <c r="E64">
-        <v>-1461.244000000001</v>
+        <v>-1392.706</v>
       </c>
       <c r="F64">
-        <v>4249.356</v>
+        <v>4317.894</v>
       </c>
       <c r="G64">
         <v>136.5</v>
@@ -6529,37 +6529,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M64">
-        <v>1001.9981448</v>
+        <v>1018.1594052</v>
       </c>
       <c r="N64">
-        <v>-913.4581448</v>
+        <v>-929.6194052000002</v>
       </c>
       <c r="O64">
-        <v>-227.81646131312</v>
+        <v>-231.8470796568801</v>
       </c>
       <c r="P64">
-        <v>-685.64168348688</v>
+        <v>-697.7723255431201</v>
       </c>
       <c r="Q64">
-        <v>-688.78168348688</v>
+        <v>-700.9123255431201</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1050304438069426</v>
+        <v>0.1066312666125356</v>
       </c>
       <c r="T64">
-        <v>1.367908632954794</v>
+        <v>1.404879136548167</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0220378412021986</v>
+        <v>0.0216880341989891</v>
       </c>
       <c r="W64">
-        <v>0.2306034770445216</v>
+        <v>0.2306859615358784</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.08836343705773297</v>
+        <v>0.0869608428187213</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1847857244142415</v>
+        <v>0.1866857244142415</v>
       </c>
       <c r="C65">
-        <v>-3480.522508989121</v>
+        <v>-3558.512537137872</v>
       </c>
       <c r="D65">
-        <v>700.8714910108798</v>
+        <v>691.4194628621282</v>
       </c>
       <c r="E65">
-        <v>-1392.706</v>
+        <v>-1324.168000000001</v>
       </c>
       <c r="F65">
-        <v>4317.894</v>
+        <v>4386.432</v>
       </c>
       <c r="G65">
         <v>136.5</v>
@@ -6611,37 +6611,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M65">
-        <v>1018.1594052</v>
+        <v>1034.3206656</v>
       </c>
       <c r="N65">
-        <v>-929.6194052000002</v>
+        <v>-945.7806656</v>
       </c>
       <c r="O65">
-        <v>-231.8470796568801</v>
+        <v>-235.87769800064</v>
       </c>
       <c r="P65">
-        <v>-697.7723255431201</v>
+        <v>-709.90296759936</v>
       </c>
       <c r="Q65">
-        <v>-700.9123255431201</v>
+        <v>-713.0429675993599</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1066312666125356</v>
+        <v>0.1083210240184394</v>
       </c>
       <c r="T65">
-        <v>1.404879136548167</v>
+        <v>1.443903557007839</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0216880341989891</v>
+        <v>0.0213491586646299</v>
       </c>
       <c r="W65">
-        <v>0.2306859615358784</v>
+        <v>0.2307658683868803</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.0869608428187213</v>
+        <v>0.08560207964967881</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1866857244142415</v>
+        <v>0.1885857244142416</v>
       </c>
       <c r="C66">
-        <v>-3558.512537137872</v>
+        <v>-3636.25101558085</v>
       </c>
       <c r="D66">
-        <v>691.4194628621282</v>
+        <v>682.218984419151</v>
       </c>
       <c r="E66">
-        <v>-1324.168000000001</v>
+        <v>-1255.63</v>
       </c>
       <c r="F66">
-        <v>4386.432</v>
+        <v>4454.97</v>
       </c>
       <c r="G66">
         <v>136.5</v>
@@ -6693,37 +6693,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M66">
-        <v>1034.3206656</v>
+        <v>1050.481926</v>
       </c>
       <c r="N66">
-        <v>-945.7806656</v>
+        <v>-961.9419260000002</v>
       </c>
       <c r="O66">
-        <v>-235.87769800064</v>
+        <v>-239.9083163444</v>
       </c>
       <c r="P66">
-        <v>-709.90296759936</v>
+        <v>-722.0336096556001</v>
       </c>
       <c r="Q66">
-        <v>-713.0429675993599</v>
+        <v>-725.1736096556001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1083210240184394</v>
+        <v>0.1101073389903948</v>
       </c>
       <c r="T66">
-        <v>1.443903557007839</v>
+        <v>1.48515794435092</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0213491586646299</v>
+        <v>0.02102071006978944</v>
       </c>
       <c r="W66">
-        <v>0.2307658683868803</v>
+        <v>0.2308433165655437</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08560207964967881</v>
+        <v>0.08428512457814519</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1885857244142416</v>
+        <v>0.1904857244142416</v>
       </c>
       <c r="C67">
-        <v>-3636.25101558085</v>
+        <v>-3713.747854302804</v>
       </c>
       <c r="D67">
-        <v>682.218984419151</v>
+        <v>673.2601456971967</v>
       </c>
       <c r="E67">
-        <v>-1255.63</v>
+        <v>-1187.092</v>
       </c>
       <c r="F67">
-        <v>4454.97</v>
+        <v>4523.508000000001</v>
       </c>
       <c r="G67">
         <v>136.5</v>
@@ -6775,37 +6775,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M67">
-        <v>1050.481926</v>
+        <v>1066.6431864</v>
       </c>
       <c r="N67">
-        <v>-961.9419260000002</v>
+        <v>-978.1031864000001</v>
       </c>
       <c r="O67">
-        <v>-239.9083163444</v>
+        <v>-243.93893468816</v>
       </c>
       <c r="P67">
-        <v>-722.0336096556001</v>
+        <v>-734.1642517118401</v>
       </c>
       <c r="Q67">
-        <v>-725.1736096556001</v>
+        <v>-737.30425171184</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1101073389903948</v>
+        <v>0.1119987313136417</v>
       </c>
       <c r="T67">
-        <v>1.48515794435092</v>
+        <v>1.528839060361241</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02102071006978944</v>
+        <v>0.02070221446267142</v>
       </c>
       <c r="W67">
-        <v>0.2308433165655437</v>
+        <v>0.2309184178297021</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08428512457814519</v>
+        <v>0.08300807723605208</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1904857244142416</v>
+        <v>0.1923857244142416</v>
       </c>
       <c r="C68">
-        <v>-3713.747854302804</v>
+        <v>-3791.012449487542</v>
       </c>
       <c r="D68">
-        <v>673.2601456971967</v>
+        <v>664.5335505124584</v>
       </c>
       <c r="E68">
-        <v>-1187.092</v>
+        <v>-1118.554</v>
       </c>
       <c r="F68">
-        <v>4523.508000000001</v>
+        <v>4592.046</v>
       </c>
       <c r="G68">
         <v>136.5</v>
@@ -6857,37 +6857,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M68">
-        <v>1066.6431864</v>
+        <v>1082.8044468</v>
       </c>
       <c r="N68">
-        <v>-978.1031864000001</v>
+        <v>-994.2644468000001</v>
       </c>
       <c r="O68">
-        <v>-243.93893468816</v>
+        <v>-247.96955303192</v>
       </c>
       <c r="P68">
-        <v>-734.1642517118401</v>
+        <v>-746.2948937680801</v>
       </c>
       <c r="Q68">
-        <v>-737.30425171184</v>
+        <v>-749.4348937680801</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1119987313136417</v>
+        <v>0.1140047534746612</v>
       </c>
       <c r="T68">
-        <v>1.528839060361241</v>
+        <v>1.575167516735824</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02070221446267142</v>
+        <v>0.02039322618710915</v>
       </c>
       <c r="W68">
-        <v>0.2309184178297021</v>
+        <v>0.2309912772650797</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08300807723605208</v>
+        <v>0.0817691507101409</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1923857244142416</v>
+        <v>0.1942857244142416</v>
       </c>
       <c r="C69">
-        <v>-3791.012449487542</v>
+        <v>-3868.053716390503</v>
       </c>
       <c r="D69">
-        <v>664.5335505124584</v>
+        <v>656.030283609498</v>
       </c>
       <c r="E69">
-        <v>-1118.554</v>
+        <v>-1050.016</v>
       </c>
       <c r="F69">
-        <v>4592.046</v>
+        <v>4660.584000000001</v>
       </c>
       <c r="G69">
         <v>136.5</v>
@@ -6939,37 +6939,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M69">
-        <v>1082.8044468</v>
+        <v>1098.9657072</v>
       </c>
       <c r="N69">
-        <v>-994.2644468000001</v>
+        <v>-1010.4257072</v>
       </c>
       <c r="O69">
-        <v>-247.96955303192</v>
+        <v>-252.0001713756801</v>
       </c>
       <c r="P69">
-        <v>-746.2948937680801</v>
+        <v>-758.4255358243201</v>
       </c>
       <c r="Q69">
-        <v>-749.4348937680801</v>
+        <v>-761.5655358243201</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1140047534746612</v>
+        <v>0.1161361520207443</v>
       </c>
       <c r="T69">
-        <v>1.575167516735824</v>
+        <v>1.624391501633819</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02039322618710915</v>
+        <v>0.0200933258020046</v>
       </c>
       <c r="W69">
-        <v>0.2309912772650797</v>
+        <v>0.2310619937758873</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.0817691507101409</v>
+        <v>0.08056666319969763</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1942857244142416</v>
+        <v>0.1961857244142416</v>
       </c>
       <c r="C70">
-        <v>-3868.053716390503</v>
+        <v>-3944.880119719429</v>
       </c>
       <c r="D70">
-        <v>656.030283609498</v>
+        <v>647.7418802805714</v>
       </c>
       <c r="E70">
-        <v>-1050.016</v>
+        <v>-981.4780000000001</v>
       </c>
       <c r="F70">
-        <v>4660.584000000001</v>
+        <v>4729.122</v>
       </c>
       <c r="G70">
         <v>136.5</v>
@@ -7021,37 +7021,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M70">
-        <v>1098.9657072</v>
+        <v>1115.1269676</v>
       </c>
       <c r="N70">
-        <v>-1010.4257072</v>
+        <v>-1026.5869676</v>
       </c>
       <c r="O70">
-        <v>-252.0001713756801</v>
+        <v>-256.0307897194401</v>
       </c>
       <c r="P70">
-        <v>-758.4255358243201</v>
+        <v>-770.5561778805602</v>
       </c>
       <c r="Q70">
-        <v>-761.5655358243201</v>
+        <v>-773.6961778805602</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1161361520207443</v>
+        <v>0.1184050601504458</v>
       </c>
       <c r="T70">
-        <v>1.624391501633819</v>
+        <v>1.676791227492974</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0200933258020046</v>
+        <v>0.0198021181816857</v>
       </c>
       <c r="W70">
-        <v>0.2310619937758873</v>
+        <v>0.2311306605327585</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08056666319969763</v>
+        <v>0.07939903039970209</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1961857244142416</v>
+        <v>0.1980857244142415</v>
       </c>
       <c r="C71">
-        <v>-3944.880119719429</v>
+        <v>-4021.49970174077</v>
       </c>
       <c r="D71">
-        <v>647.7418802805714</v>
+        <v>639.6602982592302</v>
       </c>
       <c r="E71">
-        <v>-981.4780000000001</v>
+        <v>-912.9399999999996</v>
       </c>
       <c r="F71">
-        <v>4729.122</v>
+        <v>4797.660000000001</v>
       </c>
       <c r="G71">
         <v>136.5</v>
@@ -7103,37 +7103,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M71">
-        <v>1115.1269676</v>
+        <v>1131.288228</v>
       </c>
       <c r="N71">
-        <v>-1026.5869676</v>
+        <v>-1042.748228</v>
       </c>
       <c r="O71">
-        <v>-256.0307897194401</v>
+        <v>-260.0614080632001</v>
       </c>
       <c r="P71">
-        <v>-770.5561778805602</v>
+        <v>-782.6868199368</v>
       </c>
       <c r="Q71">
-        <v>-773.6961778805602</v>
+        <v>-785.8268199368</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1184050601504458</v>
+        <v>0.1208252288221273</v>
       </c>
       <c r="T71">
-        <v>1.676791227492974</v>
+        <v>1.732684268409407</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0198021181816857</v>
+        <v>0.01951923077909019</v>
       </c>
       <c r="W71">
-        <v>0.2311306605327585</v>
+        <v>0.2311973653822905</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.07939903039970209</v>
+        <v>0.07826475853684911</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1980857244142415</v>
+        <v>0.1999857244142416</v>
       </c>
       <c r="C72">
-        <v>-4021.49970174077</v>
+        <v>-4097.920108307978</v>
       </c>
       <c r="D72">
-        <v>639.6602982592302</v>
+        <v>631.7778916920222</v>
       </c>
       <c r="E72">
-        <v>-912.9399999999996</v>
+        <v>-844.402</v>
       </c>
       <c r="F72">
-        <v>4797.660000000001</v>
+        <v>4866.198</v>
       </c>
       <c r="G72">
         <v>136.5</v>
@@ -7185,37 +7185,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M72">
-        <v>1131.288228</v>
+        <v>1147.4494884</v>
       </c>
       <c r="N72">
-        <v>-1042.748228</v>
+        <v>-1058.9094884</v>
       </c>
       <c r="O72">
-        <v>-260.0614080632001</v>
+        <v>-264.09202640696</v>
       </c>
       <c r="P72">
-        <v>-782.6868199368</v>
+        <v>-794.8174619930401</v>
       </c>
       <c r="Q72">
-        <v>-785.8268199368</v>
+        <v>-797.9574619930401</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1208252288221273</v>
+        <v>0.1234123056780627</v>
       </c>
       <c r="T72">
-        <v>1.732684268409407</v>
+        <v>1.792432001802835</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01951923077909019</v>
+        <v>0.01924431203572272</v>
       </c>
       <c r="W72">
-        <v>0.2311973653822905</v>
+        <v>0.2312621912219766</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.07826475853684911</v>
+        <v>0.07716243799407663</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1999857244142415</v>
+        <v>0.2018857244142416</v>
       </c>
       <c r="C73">
-        <v>-4097.920108307978</v>
+        <v>-4174.148612988784</v>
       </c>
       <c r="D73">
-        <v>631.7778916920222</v>
+        <v>624.0873870112151</v>
       </c>
       <c r="E73">
-        <v>-844.402</v>
+        <v>-775.8640000000005</v>
       </c>
       <c r="F73">
-        <v>4866.198</v>
+        <v>4934.736</v>
       </c>
       <c r="G73">
         <v>136.5</v>
@@ -7267,37 +7267,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M73">
-        <v>1147.4494884</v>
+        <v>1163.6107488</v>
       </c>
       <c r="N73">
-        <v>-1058.9094884</v>
+        <v>-1075.0707488</v>
       </c>
       <c r="O73">
-        <v>-264.09202640696</v>
+        <v>-268.12264475072</v>
       </c>
       <c r="P73">
-        <v>-794.8174619930401</v>
+        <v>-806.94810404928</v>
       </c>
       <c r="Q73">
-        <v>-797.9574619930401</v>
+        <v>-810.08810404928</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1234123056780627</v>
+        <v>0.1261841737379935</v>
       </c>
       <c r="T73">
-        <v>1.792432001802834</v>
+        <v>1.85644743043865</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01924431203572272</v>
+        <v>0.01897702992411546</v>
       </c>
       <c r="W73">
-        <v>0.2312621912219766</v>
+        <v>0.2313252163438936</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.07716243799407663</v>
+        <v>0.07609073746638118</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2018857244142416</v>
+        <v>0.2037857244142416</v>
       </c>
       <c r="C74">
-        <v>-4174.148612988784</v>
+        <v>-4250.192139451494</v>
       </c>
       <c r="D74">
-        <v>624.0873870112151</v>
+        <v>616.5818605485069</v>
       </c>
       <c r="E74">
-        <v>-775.8640000000005</v>
+        <v>-707.326</v>
       </c>
       <c r="F74">
-        <v>4934.736</v>
+        <v>5003.274</v>
       </c>
       <c r="G74">
         <v>136.5</v>
@@ -7349,37 +7349,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M74">
-        <v>1163.6107488</v>
+        <v>1179.7720092</v>
       </c>
       <c r="N74">
-        <v>-1075.0707488</v>
+        <v>-1091.2320092</v>
       </c>
       <c r="O74">
-        <v>-268.12264475072</v>
+        <v>-272.1532630944801</v>
       </c>
       <c r="P74">
-        <v>-806.94810404928</v>
+        <v>-819.0787461055202</v>
       </c>
       <c r="Q74">
-        <v>-810.08810404928</v>
+        <v>-822.2187461055202</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1261841737379935</v>
+        <v>0.1291613653579192</v>
       </c>
       <c r="T74">
-        <v>1.85644743043865</v>
+        <v>1.925204742677118</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01897702992411546</v>
+        <v>0.01871707061008648</v>
       </c>
       <c r="W74">
-        <v>0.2313252163438936</v>
+        <v>0.2313865147501416</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.07609073746638118</v>
+        <v>0.07504839859697865</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2037857244142416</v>
+        <v>0.2056857244142415</v>
       </c>
       <c r="C75">
-        <v>-4250.192139451494</v>
+        <v>-4326.057282255106</v>
       </c>
       <c r="D75">
-        <v>616.5818605485069</v>
+        <v>609.254717744894</v>
       </c>
       <c r="E75">
-        <v>-707.326</v>
+        <v>-638.7880000000005</v>
       </c>
       <c r="F75">
-        <v>5003.274</v>
+        <v>5071.812</v>
       </c>
       <c r="G75">
         <v>136.5</v>
@@ -7431,37 +7431,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M75">
-        <v>1179.7720092</v>
+        <v>1195.9332696</v>
       </c>
       <c r="N75">
-        <v>-1091.2320092</v>
+        <v>-1107.3932696</v>
       </c>
       <c r="O75">
-        <v>-272.1532630944801</v>
+        <v>-276.1838814382401</v>
       </c>
       <c r="P75">
-        <v>-819.0787461055202</v>
+        <v>-831.2093881617601</v>
       </c>
       <c r="Q75">
-        <v>-822.2187461055202</v>
+        <v>-834.3493881617601</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1291613653579192</v>
+        <v>0.1323675717178392</v>
       </c>
       <c r="T75">
-        <v>1.925204742677118</v>
+        <v>1.99925107893393</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01871707061008648</v>
+        <v>0.01846413722346369</v>
       </c>
       <c r="W75">
-        <v>0.2313865147501416</v>
+        <v>0.2314461564427072</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07504839859697865</v>
+        <v>0.07403423104837081</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2056857244142415</v>
+        <v>0.2075857244142416</v>
       </c>
       <c r="C76">
-        <v>-4326.057282255106</v>
+        <v>-4401.750326174502</v>
       </c>
       <c r="D76">
-        <v>609.254717744894</v>
+        <v>602.0996738254978</v>
       </c>
       <c r="E76">
-        <v>-638.7880000000005</v>
+        <v>-570.25</v>
       </c>
       <c r="F76">
-        <v>5071.812</v>
+        <v>5140.35</v>
       </c>
       <c r="G76">
         <v>136.5</v>
@@ -7513,37 +7513,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M76">
-        <v>1195.9332696</v>
+        <v>1212.09453</v>
       </c>
       <c r="N76">
-        <v>-1107.3932696</v>
+        <v>-1123.55453</v>
       </c>
       <c r="O76">
-        <v>-276.1838814382401</v>
+        <v>-280.214499782</v>
       </c>
       <c r="P76">
-        <v>-831.2093881617601</v>
+        <v>-843.340030218</v>
       </c>
       <c r="Q76">
-        <v>-834.3493881617601</v>
+        <v>-846.480030218</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1323675717178392</v>
+        <v>0.1358302745865528</v>
       </c>
       <c r="T76">
-        <v>1.99925107893393</v>
+        <v>2.079221122091288</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01846413722346369</v>
+        <v>0.01821794872715084</v>
       </c>
       <c r="W76">
-        <v>0.2314461564427072</v>
+        <v>0.2315042076901378</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07403423104837081</v>
+        <v>0.07304710796772584</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2075857244142416</v>
+        <v>0.2094857244142416</v>
       </c>
       <c r="C77">
-        <v>-4401.750326174502</v>
+        <v>-4477.277264179709</v>
       </c>
       <c r="D77">
-        <v>602.0996738254978</v>
+        <v>595.1107358202911</v>
       </c>
       <c r="E77">
-        <v>-570.25</v>
+        <v>-501.7120000000004</v>
       </c>
       <c r="F77">
-        <v>5140.35</v>
+        <v>5208.888</v>
       </c>
       <c r="G77">
         <v>136.5</v>
@@ -7595,37 +7595,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M77">
-        <v>1212.09453</v>
+        <v>1228.2557904</v>
       </c>
       <c r="N77">
-        <v>-1123.55453</v>
+        <v>-1139.7157904</v>
       </c>
       <c r="O77">
-        <v>-280.214499782</v>
+        <v>-284.24511812576</v>
       </c>
       <c r="P77">
-        <v>-843.340030218</v>
+        <v>-855.4706722742401</v>
       </c>
       <c r="Q77">
-        <v>-846.480030218</v>
+        <v>-858.6106722742401</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1358302745865528</v>
+        <v>0.1395815360276591</v>
       </c>
       <c r="T77">
-        <v>2.079221122091288</v>
+        <v>2.165855335511758</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01821794872715084</v>
+        <v>0.01797823887547781</v>
       </c>
       <c r="W77">
-        <v>0.2315042076901378</v>
+        <v>0.2315607312731623</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07304710796772584</v>
+        <v>0.07208596181025584</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2094857244142416</v>
+        <v>0.2113857244142416</v>
       </c>
       <c r="C78">
-        <v>-4477.277264179709</v>
+        <v>-4552.643814177352</v>
       </c>
       <c r="D78">
-        <v>595.1107358202911</v>
+        <v>588.2821858226483</v>
       </c>
       <c r="E78">
-        <v>-501.7120000000004</v>
+        <v>-433.174</v>
       </c>
       <c r="F78">
-        <v>5208.888</v>
+        <v>5277.426</v>
       </c>
       <c r="G78">
         <v>136.5</v>
@@ -7677,37 +7677,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M78">
-        <v>1228.2557904</v>
+        <v>1244.4170508</v>
       </c>
       <c r="N78">
-        <v>-1139.7157904</v>
+        <v>-1155.8770508</v>
       </c>
       <c r="O78">
-        <v>-284.24511812576</v>
+        <v>-288.2757364695201</v>
       </c>
       <c r="P78">
-        <v>-855.4706722742401</v>
+        <v>-867.6013143304801</v>
       </c>
       <c r="Q78">
-        <v>-858.6106722742401</v>
+        <v>-870.7413143304801</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1395815360276591</v>
+        <v>0.1436589941158182</v>
       </c>
       <c r="T78">
-        <v>2.165855335511758</v>
+        <v>2.260022958794878</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01797823887547781</v>
+        <v>0.01774475525371835</v>
       </c>
       <c r="W78">
-        <v>0.2315607312731623</v>
+        <v>0.2316157867111732</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07208596181025584</v>
+        <v>0.07114978048804466</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2113857244142416</v>
+        <v>0.2132857244142415</v>
       </c>
       <c r="C79">
-        <v>-4552.643814177352</v>
+        <v>-4627.855434612598</v>
       </c>
       <c r="D79">
-        <v>588.2821858226483</v>
+        <v>581.6085653874014</v>
       </c>
       <c r="E79">
-        <v>-433.174</v>
+        <v>-364.6360000000004</v>
       </c>
       <c r="F79">
-        <v>5277.426</v>
+        <v>5345.964</v>
       </c>
       <c r="G79">
         <v>136.5</v>
@@ -7759,37 +7759,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M79">
-        <v>1244.4170508</v>
+        <v>1260.5783112</v>
       </c>
       <c r="N79">
-        <v>-1155.8770508</v>
+        <v>-1172.0383112</v>
       </c>
       <c r="O79">
-        <v>-288.2757364695201</v>
+        <v>-292.3063548132801</v>
       </c>
       <c r="P79">
-        <v>-867.6013143304801</v>
+        <v>-879.7319563867202</v>
       </c>
       <c r="Q79">
-        <v>-870.7413143304801</v>
+        <v>-882.8719563867202</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1436589941158182</v>
+        <v>0.1481071302119918</v>
       </c>
       <c r="T79">
-        <v>2.260022958794878</v>
+        <v>2.362751275103736</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01774475525371835</v>
+        <v>0.0175172583914912</v>
       </c>
       <c r="W79">
-        <v>0.2316157867111732</v>
+        <v>0.2316694304712864</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07114978048804466</v>
+        <v>0.07023760381512101</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2132857244142415</v>
+        <v>0.2151857244142416</v>
       </c>
       <c r="C80">
-        <v>-4627.855434612598</v>
+        <v>-4702.917339021058</v>
       </c>
       <c r="D80">
-        <v>581.6085653874014</v>
+        <v>575.0846609789425</v>
       </c>
       <c r="E80">
-        <v>-364.6360000000004</v>
+        <v>-296.098</v>
       </c>
       <c r="F80">
-        <v>5345.964</v>
+        <v>5414.502</v>
       </c>
       <c r="G80">
         <v>136.5</v>
@@ -7841,37 +7841,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M80">
-        <v>1260.5783112</v>
+        <v>1276.7395716</v>
       </c>
       <c r="N80">
-        <v>-1172.0383112</v>
+        <v>-1188.1995716</v>
       </c>
       <c r="O80">
-        <v>-292.3063548132801</v>
+        <v>-296.3369731570401</v>
       </c>
       <c r="P80">
-        <v>-879.7319563867202</v>
+        <v>-891.86259844296</v>
       </c>
       <c r="Q80">
-        <v>-882.8719563867202</v>
+        <v>-895.00259844296</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1481071302119918</v>
+        <v>0.1529788983173247</v>
       </c>
       <c r="T80">
-        <v>2.362751275103736</v>
+        <v>2.475263240584867</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0175172583914912</v>
+        <v>0.01729552094349764</v>
       </c>
       <c r="W80">
-        <v>0.2316694304712864</v>
+        <v>0.2317217161615233</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07023760381512101</v>
+        <v>0.06934852022252458</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2151857244142416</v>
+        <v>0.2170857244142416</v>
       </c>
       <c r="C81">
-        <v>-4702.917339021058</v>
+        <v>-4777.834509612167</v>
       </c>
       <c r="D81">
-        <v>575.0846609789425</v>
+        <v>568.7054903878342</v>
       </c>
       <c r="E81">
-        <v>-296.098</v>
+        <v>-227.5599999999995</v>
       </c>
       <c r="F81">
-        <v>5414.502</v>
+        <v>5483.040000000001</v>
       </c>
       <c r="G81">
         <v>136.5</v>
@@ -7923,37 +7923,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M81">
-        <v>1276.7395716</v>
+        <v>1292.900832</v>
       </c>
       <c r="N81">
-        <v>-1188.1995716</v>
+        <v>-1204.360832</v>
       </c>
       <c r="O81">
-        <v>-296.3369731570401</v>
+        <v>-300.3675915008001</v>
       </c>
       <c r="P81">
-        <v>-891.86259844296</v>
+        <v>-903.9932404992003</v>
       </c>
       <c r="Q81">
-        <v>-895.00259844296</v>
+        <v>-907.1332404992003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1529788983173247</v>
+        <v>0.1583378432331909</v>
       </c>
       <c r="T81">
-        <v>2.475263240584867</v>
+        <v>2.59902640261411</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01729552094349764</v>
+        <v>0.01707932693170391</v>
       </c>
       <c r="W81">
-        <v>0.2317217161615233</v>
+        <v>0.2317726947095042</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.06934852022252458</v>
+        <v>0.06848166371974296</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2170857244142416</v>
+        <v>0.2189857244142416</v>
       </c>
       <c r="C82">
-        <v>-4777.834509612167</v>
+        <v>-4852.611709958451</v>
       </c>
       <c r="D82">
-        <v>568.7054903878342</v>
+        <v>562.4662900415497</v>
       </c>
       <c r="E82">
-        <v>-227.5599999999995</v>
+        <v>-159.0219999999999</v>
       </c>
       <c r="F82">
-        <v>5483.040000000001</v>
+        <v>5551.578</v>
       </c>
       <c r="G82">
         <v>136.5</v>
@@ -8005,37 +8005,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M82">
-        <v>1292.900832</v>
+        <v>1309.0620924</v>
       </c>
       <c r="N82">
-        <v>-1204.360832</v>
+        <v>-1220.5220924</v>
       </c>
       <c r="O82">
-        <v>-300.3675915008001</v>
+        <v>-304.3982098445601</v>
       </c>
       <c r="P82">
-        <v>-903.9932404992003</v>
+        <v>-916.1238825554401</v>
       </c>
       <c r="Q82">
-        <v>-907.1332404992003</v>
+        <v>-919.2638825554401</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1583378432331909</v>
+        <v>0.1642608876138852</v>
       </c>
       <c r="T82">
-        <v>2.59902640261411</v>
+        <v>2.735817265909589</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01707932693170391</v>
+        <v>0.01686847104365819</v>
       </c>
       <c r="W82">
-        <v>0.2317726947095042</v>
+        <v>0.2318224145279054</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.06848166371974296</v>
+        <v>0.06763621108122764</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2189857244142416</v>
+        <v>0.2208857244142416</v>
       </c>
       <c r="C83">
-        <v>-4852.611709958451</v>
+        <v>-4927.253496858579</v>
       </c>
       <c r="D83">
-        <v>562.4662900415497</v>
+        <v>556.3625031414226</v>
       </c>
       <c r="E83">
-        <v>-159.0219999999999</v>
+        <v>-90.48399999999947</v>
       </c>
       <c r="F83">
-        <v>5551.578</v>
+        <v>5620.116000000001</v>
       </c>
       <c r="G83">
         <v>136.5</v>
@@ -8087,37 +8087,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M83">
-        <v>1309.0620924</v>
+        <v>1325.2233528</v>
       </c>
       <c r="N83">
-        <v>-1220.5220924</v>
+        <v>-1236.6833528</v>
       </c>
       <c r="O83">
-        <v>-304.3982098445601</v>
+        <v>-308.42882818832</v>
       </c>
       <c r="P83">
-        <v>-916.1238825554401</v>
+        <v>-928.2545246116802</v>
       </c>
       <c r="Q83">
-        <v>-919.2638825554401</v>
+        <v>-931.3945246116801</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1642608876138852</v>
+        <v>0.1708420480368789</v>
       </c>
       <c r="T83">
-        <v>2.735817265909589</v>
+        <v>2.887807114015678</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01686847104365819</v>
+        <v>0.01666275798215016</v>
       </c>
       <c r="W83">
-        <v>0.2318224145279054</v>
+        <v>0.231870921667809</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.06763621108122764</v>
+        <v>0.06681137923877367</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2208857244142416</v>
+        <v>0.2227857244142416</v>
       </c>
       <c r="C84">
-        <v>-4927.253496858579</v>
+        <v>-5001.764231436281</v>
       </c>
       <c r="D84">
-        <v>556.3625031414226</v>
+        <v>550.3897685637197</v>
       </c>
       <c r="E84">
-        <v>-90.48399999999947</v>
+        <v>-21.94599999999991</v>
       </c>
       <c r="F84">
-        <v>5620.116000000001</v>
+        <v>5688.654</v>
       </c>
       <c r="G84">
         <v>136.5</v>
@@ -8169,37 +8169,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M84">
-        <v>1325.2233528</v>
+        <v>1341.3846132</v>
       </c>
       <c r="N84">
-        <v>-1236.6833528</v>
+        <v>-1252.8446132</v>
       </c>
       <c r="O84">
-        <v>-308.42882818832</v>
+        <v>-312.4594465320801</v>
       </c>
       <c r="P84">
-        <v>-928.2545246116802</v>
+        <v>-940.3851666679201</v>
       </c>
       <c r="Q84">
-        <v>-931.3945246116801</v>
+        <v>-943.5251666679201</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1708420480368789</v>
+        <v>0.1781974626272835</v>
       </c>
       <c r="T84">
-        <v>2.887807114015678</v>
+        <v>3.057678120722483</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01666275798215016</v>
+        <v>0.01646200186188329</v>
       </c>
       <c r="W84">
-        <v>0.231870921667809</v>
+        <v>0.2319182599609679</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06681137923877367</v>
+        <v>0.06600642286240288</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2227857244142416</v>
+        <v>0.2246857244142416</v>
       </c>
       <c r="C85">
-        <v>-5001.764231436281</v>
+        <v>-5076.148089531975</v>
       </c>
       <c r="D85">
-        <v>550.3897685637197</v>
+        <v>544.543910468026</v>
       </c>
       <c r="E85">
-        <v>-21.94599999999991</v>
+        <v>46.59200000000055</v>
       </c>
       <c r="F85">
-        <v>5688.654</v>
+        <v>5757.192000000001</v>
       </c>
       <c r="G85">
         <v>136.5</v>
@@ -8251,37 +8251,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M85">
-        <v>1341.3846132</v>
+        <v>1357.5458736</v>
       </c>
       <c r="N85">
-        <v>-1252.8446132</v>
+        <v>-1269.0058736</v>
       </c>
       <c r="O85">
-        <v>-312.4594465320801</v>
+        <v>-316.4900648758401</v>
       </c>
       <c r="P85">
-        <v>-940.3851666679201</v>
+        <v>-952.5158087241603</v>
       </c>
       <c r="Q85">
-        <v>-943.5251666679201</v>
+        <v>-955.6558087241602</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1781974626272835</v>
+        <v>0.1864723040414887</v>
       </c>
       <c r="T85">
-        <v>3.057678120722483</v>
+        <v>3.248783003267639</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01646200186188329</v>
+        <v>0.01626602564924182</v>
       </c>
       <c r="W85">
-        <v>0.2319182599609679</v>
+        <v>0.2319644711519088</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06600642286240288</v>
+        <v>0.06522063211404094</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2246857244142416</v>
+        <v>0.2265857244142415</v>
       </c>
       <c r="C86">
-        <v>-5076.148089531974</v>
+        <v>-5150.4090714391</v>
       </c>
       <c r="D86">
-        <v>544.543910468026</v>
+        <v>538.8209285609001</v>
       </c>
       <c r="E86">
-        <v>46.59199999999964</v>
+        <v>115.1299999999992</v>
       </c>
       <c r="F86">
-        <v>5757.192</v>
+        <v>5825.73</v>
       </c>
       <c r="G86">
         <v>136.5</v>
@@ -8333,37 +8333,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M86">
-        <v>1357.5458736</v>
+        <v>1373.707134</v>
       </c>
       <c r="N86">
-        <v>-1269.0058736</v>
+        <v>-1285.167134</v>
       </c>
       <c r="O86">
-        <v>-316.4900648758401</v>
+        <v>-320.5206832196</v>
       </c>
       <c r="P86">
-        <v>-952.51580872416</v>
+        <v>-964.6464507804001</v>
       </c>
       <c r="Q86">
-        <v>-955.65580872416</v>
+        <v>-967.7864507804001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1864723040414886</v>
+        <v>0.1958504576442545</v>
       </c>
       <c r="T86">
-        <v>3.248783003267636</v>
+        <v>3.465368536818812</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01626602564924183</v>
+        <v>0.01607466064160368</v>
       </c>
       <c r="W86">
-        <v>0.2319644711519088</v>
+        <v>0.2320095950207099</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06522063211404094</v>
+        <v>0.0644533305597581</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2265857244142415</v>
+        <v>0.2284857244142416</v>
       </c>
       <c r="C87">
-        <v>-5150.4090714391</v>
+        <v>-5224.551011032892</v>
       </c>
       <c r="D87">
-        <v>538.8209285609001</v>
+        <v>533.2169889671072</v>
       </c>
       <c r="E87">
-        <v>115.1299999999992</v>
+        <v>183.6679999999997</v>
       </c>
       <c r="F87">
-        <v>5825.73</v>
+        <v>5894.268</v>
       </c>
       <c r="G87">
         <v>136.5</v>
@@ -8415,37 +8415,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M87">
-        <v>1373.707134</v>
+        <v>1389.8683944</v>
       </c>
       <c r="N87">
-        <v>-1285.167134</v>
+        <v>-1301.3283944</v>
       </c>
       <c r="O87">
-        <v>-320.5206832196</v>
+        <v>-324.5513015633601</v>
       </c>
       <c r="P87">
-        <v>-964.6464507804001</v>
+        <v>-976.7770928366401</v>
       </c>
       <c r="Q87">
-        <v>-967.7864507804001</v>
+        <v>-979.9170928366401</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1958504576442545</v>
+        <v>0.206568347475987</v>
       </c>
       <c r="T87">
-        <v>3.465368536818812</v>
+        <v>3.712894860877299</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01607466064160368</v>
+        <v>0.01588774598298039</v>
       </c>
       <c r="W87">
-        <v>0.2320095950207099</v>
+        <v>0.2320536694972132</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.0644533305597581</v>
+        <v>0.06370387322766791</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2284857244142416</v>
+        <v>0.2303857244142416</v>
       </c>
       <c r="C88">
-        <v>-5224.551011032892</v>
+        <v>-5298.577584335365</v>
       </c>
       <c r="D88">
-        <v>533.2169889671072</v>
+        <v>527.7284156646353</v>
       </c>
       <c r="E88">
-        <v>183.6679999999997</v>
+        <v>252.2060000000001</v>
       </c>
       <c r="F88">
-        <v>5894.268</v>
+        <v>5962.806</v>
       </c>
       <c r="G88">
         <v>136.5</v>
@@ -8497,37 +8497,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M88">
-        <v>1389.8683944</v>
+        <v>1406.0296548</v>
       </c>
       <c r="N88">
-        <v>-1301.3283944</v>
+        <v>-1317.4896548</v>
       </c>
       <c r="O88">
-        <v>-324.5513015633601</v>
+        <v>-328.58191990712</v>
       </c>
       <c r="P88">
-        <v>-976.7770928366401</v>
+        <v>-988.9077348928802</v>
       </c>
       <c r="Q88">
-        <v>-979.9170928366401</v>
+        <v>-992.0477348928802</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.206568347475987</v>
+        <v>0.2189351434356784</v>
       </c>
       <c r="T88">
-        <v>3.712894860877299</v>
+        <v>3.998502157867861</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01588774598298039</v>
+        <v>0.01570512821306107</v>
       </c>
       <c r="W88">
-        <v>0.2320536694972132</v>
+        <v>0.2320967307673602</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06370387322766791</v>
+        <v>0.06297164479976369</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2303857244142416</v>
+        <v>0.2322857244142416</v>
       </c>
       <c r="C89">
-        <v>-5298.577584335365</v>
+        <v>-5372.4923175567</v>
       </c>
       <c r="D89">
-        <v>527.7284156646353</v>
+        <v>522.3516824432998</v>
       </c>
       <c r="E89">
-        <v>252.2060000000001</v>
+        <v>320.7439999999997</v>
       </c>
       <c r="F89">
-        <v>5962.806</v>
+        <v>6031.344</v>
       </c>
       <c r="G89">
         <v>136.5</v>
@@ -8579,37 +8579,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M89">
-        <v>1406.0296548</v>
+        <v>1422.1909152</v>
       </c>
       <c r="N89">
-        <v>-1317.4896548</v>
+        <v>-1333.6509152</v>
       </c>
       <c r="O89">
-        <v>-328.58191990712</v>
+        <v>-332.61253825088</v>
       </c>
       <c r="P89">
-        <v>-988.9077348928802</v>
+        <v>-1001.03837694912</v>
       </c>
       <c r="Q89">
-        <v>-992.0477348928802</v>
+        <v>-1004.17837694912</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2189351434356784</v>
+        <v>0.2333630720553182</v>
       </c>
       <c r="T89">
-        <v>3.998502157867861</v>
+        <v>4.331710671023516</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01570512821306107</v>
+        <v>0.01552666084700356</v>
       </c>
       <c r="W89">
-        <v>0.2320967307673602</v>
+        <v>0.2321388133722766</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06297164479976369</v>
+        <v>0.06225605792703914</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2322857244142416</v>
+        <v>0.2341857244142416</v>
       </c>
       <c r="C90">
-        <v>-5372.4923175567</v>
+        <v>-5446.298594650032</v>
       </c>
       <c r="D90">
-        <v>522.3516824432998</v>
+        <v>517.083405349968</v>
       </c>
       <c r="E90">
-        <v>320.7439999999997</v>
+        <v>389.2820000000002</v>
       </c>
       <c r="F90">
-        <v>6031.344</v>
+        <v>6099.882000000001</v>
       </c>
       <c r="G90">
         <v>136.5</v>
@@ -8661,37 +8661,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M90">
-        <v>1422.1909152</v>
+        <v>1438.3521756</v>
       </c>
       <c r="N90">
-        <v>-1333.6509152</v>
+        <v>-1349.8121756</v>
       </c>
       <c r="O90">
-        <v>-332.61253825088</v>
+        <v>-336.6431565946401</v>
       </c>
       <c r="P90">
-        <v>-1001.03837694912</v>
+        <v>-1013.16901900536</v>
       </c>
       <c r="Q90">
-        <v>-1004.17837694912</v>
+        <v>-1016.30901900536</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2333630720553182</v>
+        <v>0.2504142604239835</v>
       </c>
       <c r="T90">
-        <v>4.331710671023516</v>
+        <v>4.725502550207472</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01552666084700356</v>
+        <v>0.01535220398355408</v>
       </c>
       <c r="W90">
-        <v>0.2321388133722766</v>
+        <v>0.232179950300678</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06225605792703914</v>
+        <v>0.06155655165819596</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2341857244142416</v>
+        <v>0.2360857244142416</v>
       </c>
       <c r="C91">
-        <v>-5446.298594650032</v>
+        <v>-5519.999664413616</v>
       </c>
       <c r="D91">
-        <v>517.083405349968</v>
+        <v>511.9203355863838</v>
       </c>
       <c r="E91">
-        <v>389.2820000000002</v>
+        <v>457.8199999999997</v>
       </c>
       <c r="F91">
-        <v>6099.882000000001</v>
+        <v>6168.42</v>
       </c>
       <c r="G91">
         <v>136.5</v>
@@ -8743,37 +8743,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M91">
-        <v>1438.3521756</v>
+        <v>1454.513436</v>
       </c>
       <c r="N91">
-        <v>-1349.8121756</v>
+        <v>-1365.973436</v>
       </c>
       <c r="O91">
-        <v>-336.6431565946401</v>
+        <v>-340.6737749384001</v>
       </c>
       <c r="P91">
-        <v>-1013.16901900536</v>
+        <v>-1025.2996610616</v>
       </c>
       <c r="Q91">
-        <v>-1016.30901900536</v>
+        <v>-1028.4396610616</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2504142604239835</v>
+        <v>0.2708756864663819</v>
       </c>
       <c r="T91">
-        <v>4.725502550207472</v>
+        <v>5.19805280522822</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01535220398355408</v>
+        <v>0.01518162393929237</v>
       </c>
       <c r="W91">
-        <v>0.232179950300678</v>
+        <v>0.2322201730751149</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06155655165819596</v>
+        <v>0.06087258997310485</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2360857244142416</v>
+        <v>0.2379857244142416</v>
       </c>
       <c r="C92">
-        <v>-5519.999664413616</v>
+        <v>-5593.598647171721</v>
       </c>
       <c r="D92">
-        <v>511.9203355863838</v>
+        <v>506.8593528282801</v>
       </c>
       <c r="E92">
-        <v>457.8199999999997</v>
+        <v>526.3580000000002</v>
       </c>
       <c r="F92">
-        <v>6168.42</v>
+        <v>6236.958000000001</v>
       </c>
       <c r="G92">
         <v>136.5</v>
@@ -8825,37 +8825,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M92">
-        <v>1454.513436</v>
+        <v>1470.6746964</v>
       </c>
       <c r="N92">
-        <v>-1365.973436</v>
+        <v>-1382.1346964</v>
       </c>
       <c r="O92">
-        <v>-340.6737749384001</v>
+        <v>-344.7043932821601</v>
       </c>
       <c r="P92">
-        <v>-1025.2996610616</v>
+        <v>-1037.43030311784</v>
       </c>
       <c r="Q92">
-        <v>-1028.4396610616</v>
+        <v>-1040.57030311784</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2708756864663819</v>
+        <v>0.2958840960737577</v>
       </c>
       <c r="T92">
-        <v>5.19805280522822</v>
+        <v>5.775614228031356</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01518162393929237</v>
+        <v>0.01501479290699245</v>
       </c>
       <c r="W92">
-        <v>0.2322201730751149</v>
+        <v>0.2322595118325312</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06087258997310485</v>
+        <v>0.06020366041296088</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2379857244142416</v>
+        <v>0.2398857244142416</v>
       </c>
       <c r="C93">
-        <v>-5593.598647171721</v>
+        <v>-5667.098541063093</v>
       </c>
       <c r="D93">
-        <v>506.8593528282801</v>
+        <v>501.8974589369067</v>
       </c>
       <c r="E93">
-        <v>526.3580000000002</v>
+        <v>594.8959999999997</v>
       </c>
       <c r="F93">
-        <v>6236.958000000001</v>
+        <v>6305.496</v>
       </c>
       <c r="G93">
         <v>136.5</v>
@@ -8907,37 +8907,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M93">
-        <v>1470.6746964</v>
+        <v>1486.8359568</v>
       </c>
       <c r="N93">
-        <v>-1382.1346964</v>
+        <v>-1398.2959568</v>
       </c>
       <c r="O93">
-        <v>-344.7043932821601</v>
+        <v>-348.73501162592</v>
       </c>
       <c r="P93">
-        <v>-1037.43030311784</v>
+        <v>-1049.56094517408</v>
       </c>
       <c r="Q93">
-        <v>-1040.57030311784</v>
+        <v>-1052.70094517408</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2958840960737577</v>
+        <v>0.3271446080829775</v>
       </c>
       <c r="T93">
-        <v>5.775614228031356</v>
+        <v>6.497566006535277</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01501479290699245</v>
+        <v>0.01485158863626428</v>
       </c>
       <c r="W93">
-        <v>0.2322595118325312</v>
+        <v>0.2322979953995689</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06020366041296088</v>
+        <v>0.05954927279977651</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2398857244142416</v>
+        <v>0.2417857244142416</v>
       </c>
       <c r="C94">
-        <v>-5667.098541063093</v>
+        <v>-5740.502227963658</v>
       </c>
       <c r="D94">
-        <v>501.8974589369067</v>
+        <v>497.0317720363424</v>
       </c>
       <c r="E94">
-        <v>594.8959999999997</v>
+        <v>663.4340000000002</v>
       </c>
       <c r="F94">
-        <v>6305.496</v>
+        <v>6374.034000000001</v>
       </c>
       <c r="G94">
         <v>136.5</v>
@@ -8989,37 +8989,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M94">
-        <v>1486.8359568</v>
+        <v>1502.9972172</v>
       </c>
       <c r="N94">
-        <v>-1398.2959568</v>
+        <v>-1414.4572172</v>
       </c>
       <c r="O94">
-        <v>-348.73501162592</v>
+        <v>-352.7656299696801</v>
       </c>
       <c r="P94">
-        <v>-1049.56094517408</v>
+        <v>-1061.69158723032</v>
       </c>
       <c r="Q94">
-        <v>-1052.70094517408</v>
+        <v>-1064.83158723032</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3271446080829775</v>
+        <v>0.3673366949519743</v>
       </c>
       <c r="T94">
-        <v>6.497566006535277</v>
+        <v>7.425789721754604</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01485158863626428</v>
+        <v>0.01469189413479907</v>
       </c>
       <c r="W94">
-        <v>0.2322979953995689</v>
+        <v>0.2323356513630144</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.05954927279977651</v>
+        <v>0.05890895803848861</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2417857244142416</v>
+        <v>0.2436857244142416</v>
       </c>
       <c r="C95">
-        <v>-5740.502227963658</v>
+        <v>-5813.812479067999</v>
       </c>
       <c r="D95">
-        <v>497.0317720363424</v>
+        <v>492.2595209320018</v>
       </c>
       <c r="E95">
-        <v>663.4340000000002</v>
+        <v>731.9719999999998</v>
       </c>
       <c r="F95">
-        <v>6374.034000000001</v>
+        <v>6442.572</v>
       </c>
       <c r="G95">
         <v>136.5</v>
@@ -9071,37 +9071,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M95">
-        <v>1502.9972172</v>
+        <v>1519.1584776</v>
       </c>
       <c r="N95">
-        <v>-1414.4572172</v>
+        <v>-1430.6184776</v>
       </c>
       <c r="O95">
-        <v>-352.7656299696801</v>
+        <v>-356.7962483134401</v>
       </c>
       <c r="P95">
-        <v>-1061.69158723032</v>
+        <v>-1073.82222928656</v>
       </c>
       <c r="Q95">
-        <v>-1064.83158723032</v>
+        <v>-1076.96222928656</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3673366949519743</v>
+        <v>0.4209261441106367</v>
       </c>
       <c r="T95">
-        <v>7.425789721754604</v>
+        <v>8.663421342047039</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01469189413479907</v>
+        <v>0.01453559738868418</v>
       </c>
       <c r="W95">
-        <v>0.2323356513630144</v>
+        <v>0.2323725061357483</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05890895803848861</v>
+        <v>0.05828226699552597</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2436857244142416</v>
+        <v>0.2455857244142416</v>
       </c>
       <c r="C96">
-        <v>-5813.812479067999</v>
+        <v>-5887.031960152361</v>
       </c>
       <c r="D96">
-        <v>492.2595209320018</v>
+        <v>487.57803984764</v>
       </c>
       <c r="E96">
-        <v>731.9719999999998</v>
+        <v>800.5100000000002</v>
       </c>
       <c r="F96">
-        <v>6442.572</v>
+        <v>6511.110000000001</v>
       </c>
       <c r="G96">
         <v>136.5</v>
@@ -9153,37 +9153,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M96">
-        <v>1519.1584776</v>
+        <v>1535.319738</v>
       </c>
       <c r="N96">
-        <v>-1430.6184776</v>
+        <v>-1446.779738</v>
       </c>
       <c r="O96">
-        <v>-356.7962483134401</v>
+        <v>-360.8268666572001</v>
       </c>
       <c r="P96">
-        <v>-1073.82222928656</v>
+        <v>-1085.9528713428</v>
       </c>
       <c r="Q96">
-        <v>-1076.96222928656</v>
+        <v>-1089.0928713428</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4209261441106367</v>
+        <v>0.4959513729327643</v>
       </c>
       <c r="T96">
-        <v>8.663421342047039</v>
+        <v>10.39610561045645</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01453559738868418</v>
+        <v>0.01438259110038225</v>
       </c>
       <c r="W96">
-        <v>0.2323725061357483</v>
+        <v>0.2324085850185299</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.05828226699552597</v>
+        <v>0.05766876944820465</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2455857244142416</v>
+        <v>0.2474857244142416</v>
       </c>
       <c r="C97">
-        <v>-5887.031960152361</v>
+        <v>-5960.163236540172</v>
       </c>
       <c r="D97">
-        <v>487.57803984764</v>
+        <v>482.9847634598289</v>
       </c>
       <c r="E97">
-        <v>800.5100000000002</v>
+        <v>869.0480000000007</v>
       </c>
       <c r="F97">
-        <v>6511.110000000001</v>
+        <v>6579.648000000001</v>
       </c>
       <c r="G97">
         <v>136.5</v>
@@ -9235,37 +9235,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M97">
-        <v>1535.319738</v>
+        <v>1551.4809984</v>
       </c>
       <c r="N97">
-        <v>-1446.779738</v>
+        <v>-1462.9409984</v>
       </c>
       <c r="O97">
-        <v>-360.8268666572001</v>
+        <v>-364.8574850009601</v>
       </c>
       <c r="P97">
-        <v>-1085.9528713428</v>
+        <v>-1098.08351339904</v>
       </c>
       <c r="Q97">
-        <v>-1089.0928713428</v>
+        <v>-1101.22351339904</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4959513729327643</v>
+        <v>0.6084892161659556</v>
       </c>
       <c r="T97">
-        <v>10.39610561045645</v>
+        <v>12.99513201307057</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01438259110038225</v>
+        <v>0.0142327724430866</v>
       </c>
       <c r="W97">
-        <v>0.2324085850185299</v>
+        <v>0.2324439122579202</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05766876944820465</v>
+        <v>0.0570680530997858</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2474857244142415</v>
+        <v>0.2493857244142416</v>
       </c>
       <c r="C98">
-        <v>-5960.163236540171</v>
+        <v>-6033.20877778951</v>
       </c>
       <c r="D98">
-        <v>482.9847634598289</v>
+        <v>478.4772222104899</v>
       </c>
       <c r="E98">
-        <v>869.0479999999998</v>
+        <v>937.5859999999993</v>
       </c>
       <c r="F98">
-        <v>6579.648</v>
+        <v>6648.186</v>
       </c>
       <c r="G98">
         <v>136.5</v>
@@ -9317,37 +9317,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M98">
-        <v>1551.4809984</v>
+        <v>1567.6422588</v>
       </c>
       <c r="N98">
-        <v>-1462.9409984</v>
+        <v>-1479.1022588</v>
       </c>
       <c r="O98">
-        <v>-364.85748500096</v>
+        <v>-368.88810334472</v>
       </c>
       <c r="P98">
-        <v>-1098.08351339904</v>
+        <v>-1110.21415545528</v>
       </c>
       <c r="Q98">
-        <v>-1101.22351339904</v>
+        <v>-1113.35415545528</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.608489216165954</v>
+        <v>0.7960522882212722</v>
       </c>
       <c r="T98">
-        <v>12.99513201307053</v>
+        <v>17.32684268409405</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0142327724430866</v>
+        <v>0.01408604283027127</v>
       </c>
       <c r="W98">
-        <v>0.2324439122579202</v>
+        <v>0.232478511100622</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.0570680530997858</v>
+        <v>0.0564797226554582</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2493857244142416</v>
+        <v>0.2512857244142416</v>
       </c>
       <c r="C99">
-        <v>-6033.20877778951</v>
+        <v>-6106.170962120521</v>
       </c>
       <c r="D99">
-        <v>478.4772222104899</v>
+        <v>474.053037879479</v>
       </c>
       <c r="E99">
-        <v>937.5859999999993</v>
+        <v>1006.124</v>
       </c>
       <c r="F99">
-        <v>6648.186</v>
+        <v>6716.724</v>
       </c>
       <c r="G99">
         <v>136.5</v>
@@ -9399,37 +9399,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M99">
-        <v>1567.6422588</v>
+        <v>1583.8035192</v>
       </c>
       <c r="N99">
-        <v>-1479.1022588</v>
+        <v>-1495.2635192</v>
       </c>
       <c r="O99">
-        <v>-368.88810334472</v>
+        <v>-372.9187216884801</v>
       </c>
       <c r="P99">
-        <v>-1110.21415545528</v>
+        <v>-1122.34479751152</v>
       </c>
       <c r="Q99">
-        <v>-1113.35415545528</v>
+        <v>-1125.48479751152</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7960522882212722</v>
+        <v>1.171178432331908</v>
       </c>
       <c r="T99">
-        <v>17.32684268409405</v>
+        <v>25.99026402614107</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01408604283027127</v>
+        <v>0.01394230769935013</v>
       </c>
       <c r="W99">
-        <v>0.232478511100622</v>
+        <v>0.2325124038444933</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0564797226554582</v>
+        <v>0.05590339895489227</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2512857244142416</v>
+        <v>0.2531857244142416</v>
       </c>
       <c r="C100">
-        <v>-6106.170962120521</v>
+        <v>-6179.052080599457</v>
       </c>
       <c r="D100">
-        <v>474.053037879479</v>
+        <v>469.7099194005434</v>
       </c>
       <c r="E100">
-        <v>1006.124</v>
+        <v>1074.661999999999</v>
       </c>
       <c r="F100">
-        <v>6716.724</v>
+        <v>6785.262</v>
       </c>
       <c r="G100">
         <v>136.5</v>
@@ -9481,37 +9481,37 @@
         <v>88.54000000000001</v>
       </c>
       <c r="M100">
-        <v>1583.8035192</v>
+        <v>1599.9647796</v>
       </c>
       <c r="N100">
-        <v>-1495.2635192</v>
+        <v>-1511.4247796</v>
       </c>
       <c r="O100">
-        <v>-372.9187216884801</v>
+        <v>-376.94934003224</v>
       </c>
       <c r="P100">
-        <v>-1122.34479751152</v>
+        <v>-1134.47543956776</v>
       </c>
       <c r="Q100">
-        <v>-1125.48479751152</v>
+        <v>-1137.61543956776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.171178432331908</v>
+        <v>2.296556864663816</v>
       </c>
       <c r="T100">
-        <v>25.99026402614107</v>
+        <v>51.98052805228214</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01394230769935013</v>
+        <v>0.01380147630844761</v>
       </c>
       <c r="W100">
-        <v>0.2325124038444933</v>
+        <v>0.2325456118864681</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05590339895489227</v>
+        <v>0.05533871815736813</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2531857244142416</v>
-      </c>
-      <c r="C101">
-        <v>-6179.052080599457</v>
-      </c>
-      <c r="D101">
-        <v>469.7099194005434</v>
-      </c>
-      <c r="E101">
-        <v>1074.661999999999</v>
-      </c>
-      <c r="F101">
-        <v>6785.262</v>
-      </c>
-      <c r="G101">
-        <v>136.5</v>
-      </c>
-      <c r="H101">
-        <v>1143.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="K101">
-        <v>-3.14</v>
-      </c>
-      <c r="L101">
-        <v>88.54000000000001</v>
-      </c>
-      <c r="M101">
-        <v>1599.9647796</v>
-      </c>
-      <c r="N101">
-        <v>-1511.4247796</v>
-      </c>
-      <c r="O101">
-        <v>-376.94934003224</v>
-      </c>
-      <c r="P101">
-        <v>-1134.47543956776</v>
-      </c>
-      <c r="Q101">
-        <v>-1137.61543956776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.296556864663816</v>
-      </c>
-      <c r="T101">
-        <v>51.98052805228214</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01380147630844761</v>
-      </c>
-      <c r="W101">
-        <v>0.2325456118864681</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05533871815736813</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
